--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.37999999523163</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="D2715" t="n">
         <v>1.37999999523163</v>
       </c>
       <c r="E2715" t="n">
-        <v>1.37999999523163</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="F2715" t="n">
         <v>1.37999999523163</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.39999997615814</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.39999997615814</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="E2716" t="n">
-        <v>1.39999997615814</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.39999997615814</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>300</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.42999994754791</v>
+        <v>1.39999997615814</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.42999994754791</v>
+        <v>1.39999997615814</v>
       </c>
       <c r="E2717" t="n">
-        <v>1.42999994754791</v>
+        <v>1.39999997615814</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.42999994754791</v>
+        <v>1.39999997615814</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>8700</v>
+        <v>300</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.52999997138977</v>
+        <v>1.42999994754791</v>
       </c>
       <c r="D2718" t="n">
-        <v>1.38999998569489</v>
+        <v>1.42999994754791</v>
       </c>
       <c r="E2718" t="n">
-        <v>1.44000005722046</v>
+        <v>1.42999994754791</v>
       </c>
       <c r="F2718" t="n">
-        <v>1.47000002861023</v>
+        <v>1.42999994754791</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>2100</v>
+        <v>8700</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.48000001907349</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.48000001907349</v>
+        <v>1.38999998569489</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.48000001907349</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.48000001907349</v>
+        <v>1.47000002861023</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,10 +62911,10 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>5700</v>
+        <v>2100</v>
       </c>
       <c r="C2720" t="n">
         <v>1.48000001907349</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>300</v>
+        <v>5700</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.50999999046326</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.50999999046326</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.50999999046326</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.50999999046326</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,22 +62957,22 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>4800</v>
+        <v>300</v>
       </c>
       <c r="C2722" t="n">
-        <v>1.48000001907349</v>
+        <v>1.50999999046326</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.4099999666214</v>
+        <v>1.50999999046326</v>
       </c>
       <c r="E2722" t="n">
-        <v>1.48000001907349</v>
+        <v>1.50999999046326</v>
       </c>
       <c r="F2722" t="n">
-        <v>1.42999994754791</v>
+        <v>1.50999999046326</v>
       </c>
       <c r="G2722" t="s">
         <v>7</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -62978,6 +62978,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="G2724" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895930290222</v>
+        <v>2.24895906448364</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211264610291</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31634330749512</v>
+        <v>2.31634378433228</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053597450256</v>
+        <v>2.24053621292114</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G53" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831324577332</v>
+        <v>2.18831300735474</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745143890381</v>
+        <v>2.10745167732239</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.2708592414856</v>
+        <v>2.27085900306702</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G85" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G86" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G87" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.5</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.5</v>
       </c>
       <c r="G138" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.5</v>
       </c>
       <c r="G139" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.5</v>
       </c>
       <c r="G144" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078329086304</v>
+        <v>1.91078305244446</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.86735618114471</v>
+        <v>1.867356300354</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998536109924</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998536109924</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.86735618114471</v>
+        <v>1.867356300354</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.86735618114471</v>
+        <v>1.867356300354</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.86735618114471</v>
+        <v>1.867356300354</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.86735618114471</v>
+        <v>1.867356300354</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G190" t="n">
-        <v>2.21824526786804</v>
+        <v>2.21824550628662</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.43190550804138</v>
+        <v>2.43190574645996</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64903998374939</v>
+        <v>2.64904022216797</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57434558868408</v>
+        <v>2.57434606552124</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800880432129</v>
+        <v>2.41800904273987</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401784896851</v>
+        <v>2.48401761054993</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.43190550804138</v>
+        <v>2.43190574645996</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425407409668</v>
+        <v>2.28425431251526</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G235" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G247" t="n">
-        <v>2.3502631187439</v>
+        <v>2.35026335716248</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G257" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G262" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.3242073059082</v>
+        <v>2.32420706748962</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G272" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>2.61603593826294</v>
+        <v>2.61603569984436</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087182998657</v>
+        <v>2.57087159156799</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955718040466</v>
+        <v>2.57955694198608</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.63166928291321</v>
+        <v>2.63166952133179</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772557258606</v>
+        <v>2.65772533416748</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.74110507965088</v>
+        <v>2.7411048412323</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537700653076</v>
+        <v>2.80537724494934</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706664085388</v>
+        <v>2.84706711769104</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091633796692</v>
+        <v>2.90091609954834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.46546530723572</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020718574524</v>
+        <v>3.50020694732666</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.46546530723572</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G309" t="n">
-        <v>3.13194680213928</v>
+        <v>3.13194704055786</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>3.23964595794678</v>
+        <v>3.2396457195282</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480958938599</v>
+        <v>3.28480982780457</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G333" t="n">
-        <v>3.47762513160706</v>
+        <v>3.47762537002563</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706116676331</v>
+        <v>3.58706068992615</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170783996582</v>
+        <v>3.7017080783844</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339747428894</v>
+        <v>3.74339771270752</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987623214722</v>
+        <v>3.7798764705658</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G356" t="n">
-        <v>4.65769863128662</v>
+        <v>4.65769910812378</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>4.44517946243286</v>
+        <v>4.44517993927002</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G368" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G369" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>4.10160827636719</v>
+        <v>4.10160875320435</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G388" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G389" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G392" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G393" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G394" t="n">
-        <v>4.39027976989746</v>
+        <v>4.3902792930603</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G396" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G399" t="n">
-        <v>4.10515022277832</v>
+        <v>4.10514974594116</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G406" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G408" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G413" t="n">
-        <v>4.04316520690918</v>
+        <v>4.04316568374634</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G444" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5</v>
       </c>
       <c r="G447" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5</v>
       </c>
       <c r="G451" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G455" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786762237549</v>
+        <v>4.20786714553833</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G467" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G469" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G470" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G479" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G481" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G483" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G485" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G486" t="n">
-        <v>4.07858562469482</v>
+        <v>4.07858514785767</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13525724411011</v>
+        <v>4.13525772094727</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G495" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G502" t="n">
-        <v>3.95107436180115</v>
+        <v>3.95107388496399</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.8253345489502</v>
+        <v>3.82533407211304</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G524" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G538" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G541" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G542" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5</v>
       </c>
       <c r="G549" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G559" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.5</v>
       </c>
       <c r="G560" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G567" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G568" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5</v>
       </c>
       <c r="G579" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5</v>
       </c>
       <c r="G600" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5</v>
       </c>
       <c r="G601" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5</v>
       </c>
       <c r="G605" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G608" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G610" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G611" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G612" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G613" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G615" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G621" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5</v>
       </c>
       <c r="G623" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5</v>
       </c>
       <c r="G624" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5</v>
       </c>
       <c r="G627" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5</v>
       </c>
       <c r="G628" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5</v>
       </c>
       <c r="G629" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G640" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G641" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G651" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G656" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G657" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G662" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G664" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G665" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G667" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.5</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G693" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5</v>
       </c>
       <c r="G696" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G710" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G711" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G712" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5</v>
       </c>
       <c r="G714" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5</v>
       </c>
       <c r="G715" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G719" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.5</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.5</v>
       </c>
       <c r="G723" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.5</v>
       </c>
       <c r="G724" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G733" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G754" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G757" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G758" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G759" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G760" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G761" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G762" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G763" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G764" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G765" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G767" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G768" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G772" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.5</v>
       </c>
       <c r="G773" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.5</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G781" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G783" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G795" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G801" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G830" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G837" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G838" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G840" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G841" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G842" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G843" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G845" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>1.44000005722046</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0973436832428</v>
+        <v>2.09734392166138</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522847175598</v>
+        <v>2.05522871017456</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11419010162354</v>
+        <v>2.11418986320496</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11419010162354</v>
+        <v>2.11418986320496</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831300735474</v>
+        <v>2.18831324577332</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745167732239</v>
+        <v>2.10745143890381</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14788246154785</v>
+        <v>2.14788222312927</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.14788246154785</v>
+        <v>2.14788222312927</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820525169373</v>
+        <v>2.17820501327515</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G85" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G86" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G87" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G90" t="n">
-        <v>2.6038761138916</v>
+        <v>2.60387587547302</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.39716410636902</v>
+        <v>2.3971643447876</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.0410635471344</v>
+        <v>2.04106378555298</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693371295929</v>
+        <v>1.85693383216858</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693371295929</v>
+        <v>1.85693383216858</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G177" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G197" t="n">
-        <v>2.32941818237305</v>
+        <v>2.32941794395447</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57434606552124</v>
+        <v>2.57434582710266</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G204" t="n">
-        <v>2.58650517463684</v>
+        <v>2.58650541305542</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800904273987</v>
+        <v>2.41800880432129</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613042831421</v>
+        <v>2.53613018989563</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G231" t="n">
-        <v>2.20087456703186</v>
+        <v>2.20087432861328</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G240" t="n">
-        <v>2.38674163818359</v>
+        <v>2.38674139976501</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.38153052330017</v>
+        <v>2.38153076171875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G264" t="n">
-        <v>2.2251935005188</v>
+        <v>2.22519373893738</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246697425842</v>
+        <v>2.69246673583984</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.68378138542175</v>
+        <v>2.68378162384033</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.63166952133179</v>
+        <v>2.63166928291321</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>2.77063536643982</v>
+        <v>2.7706356048584</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.7411048412323</v>
+        <v>2.74110507965088</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706711769104</v>
+        <v>2.84706687927246</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091609954834</v>
+        <v>2.90091633796692</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110210418701</v>
+        <v>3.11110234260559</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020694732666</v>
+        <v>3.50020718574524</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>3.37861204147339</v>
+        <v>3.37861180305481</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34386992454529</v>
+        <v>3.34387016296387</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G333" t="n">
-        <v>3.47762537002563</v>
+        <v>3.47762513160706</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706068992615</v>
+        <v>3.58706092834473</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.7017080783844</v>
+        <v>3.70170783996582</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.7798764705658</v>
+        <v>3.77987694740295</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G339" t="n">
-        <v>3.78335046768188</v>
+        <v>3.78334999084473</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.0821270942688</v>
+        <v>4.08212757110596</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>1.4099999666214</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G3" t="n">
-        <v>2.27422833442688</v>
+        <v>2.2742280960083</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211336135864</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.09734392166138</v>
+        <v>2.09734416007996</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31634378433228</v>
+        <v>2.31634330749512</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053621292114</v>
+        <v>2.24053597450256</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G53" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831324577332</v>
+        <v>2.18831300735474</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820501327515</v>
+        <v>2.17820525169373</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G76" t="n">
-        <v>2.27422833442688</v>
+        <v>2.2742280960083</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G90" t="n">
-        <v>2.60387587547302</v>
+        <v>2.6038761138916</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G125" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>2.1887149810791</v>
+        <v>2.18871521949768</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G140" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G142" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G177" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G190" t="n">
-        <v>2.21824550628662</v>
+        <v>2.21824526786804</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G197" t="n">
-        <v>2.32941794395447</v>
+        <v>2.32941818237305</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303117752075</v>
+        <v>2.58303141593933</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G204" t="n">
-        <v>2.58650541305542</v>
+        <v>2.58650517463684</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800880432129</v>
+        <v>2.41800904273987</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613018989563</v>
+        <v>2.53612995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706961631775</v>
+        <v>2.47706937789917</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669439315796</v>
+        <v>2.42669415473938</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G230" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G235" t="n">
-        <v>2.29988789558411</v>
+        <v>2.29988813400269</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29988789558411</v>
+        <v>2.29988813400269</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G240" t="n">
-        <v>2.38674139976501</v>
+        <v>2.38674163818359</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G247" t="n">
-        <v>2.35026335716248</v>
+        <v>2.3502631187439</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>2.33462953567505</v>
+        <v>2.33462929725647</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.38153076171875</v>
+        <v>2.38153100013733</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G259" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G262" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G272" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G276" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382886886597</v>
+        <v>2.64382863044739</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246673583984</v>
+        <v>2.69246697425842</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087159156799</v>
+        <v>2.57087135314941</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955694198608</v>
+        <v>2.57955718040466</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537724494934</v>
+        <v>2.80537700653076</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706687927246</v>
+        <v>2.84706664085388</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091633796692</v>
+        <v>2.90091609954834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044341087341</v>
+        <v>3.30044364929199</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.50889229774475</v>
+        <v>3.50889253616333</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124110221863</v>
+        <v>3.36124086380005</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.75</v>
       </c>
       <c r="G310" t="n">
-        <v>3.25701642036438</v>
+        <v>3.25701665878296</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218052864075</v>
+        <v>3.30218076705933</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G327" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588777542114</v>
+        <v>3.47588801383972</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987694740295</v>
+        <v>3.77987670898438</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G341" t="n">
-        <v>3.90668296813965</v>
+        <v>3.90668272972107</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G345" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G355" t="n">
-        <v>4.39913415908813</v>
+        <v>4.39913463592529</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G356" t="n">
-        <v>4.65769910812378</v>
+        <v>4.65769863128662</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G361" t="n">
-        <v>4.34246253967285</v>
+        <v>4.34246301651001</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>4.10160875320435</v>
+        <v>4.10160827636719</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G399" t="n">
-        <v>4.10514974594116</v>
+        <v>4.10515022277832</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G401" t="n">
-        <v>4.1671347618103</v>
+        <v>4.16713428497314</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G422" t="n">
-        <v>3.94576120376587</v>
+        <v>3.94576096534729</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G446" t="n">
-        <v>4.3725700378418</v>
+        <v>4.37256956100464</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G448" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G456" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786714553833</v>
+        <v>4.20786762237549</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G481" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13525772094727</v>
+        <v>4.13525724411011</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.82533407211304</v>
+        <v>3.82533431053162</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G529" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G531" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.5</v>
       </c>
       <c r="G560" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G594" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G621" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G630" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G635" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G636" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G637" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G640" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G641" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.87846374511719</v>
+        <v>3.87846398353577</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.5</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G693" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G699" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G704" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.5</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.5</v>
       </c>
       <c r="G723" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.5</v>
       </c>
       <c r="G724" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G749" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G751" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G753" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.5</v>
       </c>
       <c r="G773" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.5</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G791" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G800" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G824" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G827" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G829" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G840" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G845" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.52999997138977</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63185,6 +63185,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.54999995231628</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.58000004291534</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.61000001430511</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.58000004291534</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>9600</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.61000001430511</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.54999995231628</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.58000004291534</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.58000004291534</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895906448364</v>
+        <v>2.24895930290222</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2287437915802</v>
+        <v>2.22874355316162</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22368979454041</v>
+        <v>2.22369003295898</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18157482147217</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18157482147217</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18157482147217</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0973436832428</v>
+        <v>2.09734392166138</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522871017456</v>
+        <v>2.05522847175598</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053597450256</v>
+        <v>2.24053621292114</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G53" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11419010162354</v>
+        <v>2.11418962478638</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11419010162354</v>
+        <v>2.11418962478638</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831276893616</v>
+        <v>2.18831324577332</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576725006104</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820525169373</v>
+        <v>2.17820501327515</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35845875740051</v>
+        <v>2.35845899581909</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G111" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G125" t="n">
-        <v>2.31031036376953</v>
+        <v>2.31031060218811</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G137" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078317165375</v>
+        <v>1.91078329086304</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683922290802</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683922290802</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.95421004295349</v>
+        <v>1.95421016216278</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>1.78050220012665</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G177" t="n">
-        <v>1.78050220012665</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.78050220012665</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.78050220012665</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.31031036376953</v>
+        <v>2.31031060218811</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138854980469</v>
+        <v>2.50138878822327</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64904022216797</v>
+        <v>2.64903998374939</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800928115845</v>
+        <v>2.41800904273987</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613018989563</v>
+        <v>2.53613042831421</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706937789917</v>
+        <v>2.47706961631775</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669415473938</v>
+        <v>2.42669439315796</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425431251526</v>
+        <v>2.28425407409668</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331512451172</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331512451172</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331512451172</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G230" t="n">
-        <v>2.31031036376953</v>
+        <v>2.31031060218811</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41453504562378</v>
+        <v>2.4145348072052</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G259" t="n">
-        <v>2.31031036376953</v>
+        <v>2.31031060218811</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382863044739</v>
+        <v>2.64382886886597</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>2.61603593826294</v>
+        <v>2.61603569984436</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087159156799</v>
+        <v>2.57087182998657</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772533416748</v>
+        <v>2.65772557258606</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110234260559</v>
+        <v>3.11110210418701</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044364929199</v>
+        <v>3.30044341087341</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020742416382</v>
+        <v>3.50020718574524</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124086380005</v>
+        <v>3.36124110221863</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23096036911011</v>
+        <v>3.23096060752869</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17016291618347</v>
+        <v>3.17016267776489</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>3.23096036911011</v>
+        <v>3.23096060752869</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>3.17016291618347</v>
+        <v>3.17016267776489</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480982780457</v>
+        <v>3.28480958938599</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34387016296387</v>
+        <v>3.34386992454529</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>3.5610044002533</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>3.5610044002533</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.4758882522583</v>
+        <v>3.47588801383972</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706092834473</v>
+        <v>3.58706116676331</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>3.5610044002533</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170783996582</v>
+        <v>3.70170760154724</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987623214722</v>
+        <v>3.77987599372864</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G340" t="n">
-        <v>3.78508710861206</v>
+        <v>3.78508734703064</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>1.55999994277954</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895930290222</v>
+        <v>2.24895906448364</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H12" t="n">
         <v>2700</v>
@@ -746,7 +746,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368955612183</v>
       </c>
       <c r="H13" t="n">
         <v>3300</v>
@@ -775,7 +775,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368955612183</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H16" t="n">
         <v>1500</v>
@@ -862,7 +862,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368955612183</v>
       </c>
       <c r="H22" t="n">
         <v>3300</v>
@@ -1123,7 +1123,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12261319160461</v>
+        <v>2.12261295318604</v>
       </c>
       <c r="H26" t="n">
         <v>1500</v>
@@ -1152,7 +1152,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.09734416007996</v>
+        <v>2.0973436832428</v>
       </c>
       <c r="H27" t="n">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522871017456</v>
+        <v>2.0552282333374</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1210,7 +1210,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1239,7 +1239,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H31" t="n">
         <v>3600</v>
@@ -1297,7 +1297,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688208580017</v>
+        <v>2.36688232421875</v>
       </c>
       <c r="H36" t="n">
         <v>1500</v>
@@ -1442,7 +1442,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3163435459137</v>
+        <v>2.31634330749512</v>
       </c>
       <c r="H37" t="n">
         <v>2400</v>
@@ -1471,7 +1471,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H38" t="n">
         <v>300</v>
@@ -1500,7 +1500,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1529,7 +1529,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053597450256</v>
+        <v>2.24053621292114</v>
       </c>
       <c r="H42" t="n">
         <v>900</v>
@@ -1616,7 +1616,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H43" t="n">
         <v>1800</v>
@@ -1645,7 +1645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H44" t="n">
         <v>12600</v>
@@ -1674,7 +1674,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12261319160461</v>
+        <v>2.12261295318604</v>
       </c>
       <c r="H47" t="n">
         <v>600</v>
@@ -1761,7 +1761,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12261319160461</v>
+        <v>2.12261295318604</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H49" t="n">
         <v>1200</v>
@@ -1935,7 +1935,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H54" t="n">
         <v>5100</v>
@@ -1964,7 +1964,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H55" t="n">
         <v>8400</v>
@@ -1993,7 +1993,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103652000427</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H56" t="n">
         <v>10200</v>
@@ -2022,7 +2022,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103652000427</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H57" t="n">
         <v>300</v>
@@ -2051,7 +2051,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103652000427</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103652000427</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H59" t="n">
         <v>116400</v>
@@ -2109,7 +2109,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H60" t="n">
         <v>235800</v>
@@ -2138,7 +2138,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H61" t="n">
         <v>2100</v>
@@ -2167,7 +2167,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831324577332</v>
+        <v>2.18831300735474</v>
       </c>
       <c r="H62" t="n">
         <v>39000</v>
@@ -2486,7 +2486,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="n">
         <v>300</v>
@@ -2515,7 +2515,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820525169373</v>
+        <v>2.17820501327515</v>
       </c>
       <c r="H75" t="n">
         <v>300</v>
@@ -2602,7 +2602,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="n">
         <v>8400</v>
@@ -2660,7 +2660,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.44268941879272</v>
+        <v>2.4426896572113</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>2.44268941879272</v>
+        <v>2.4426896572113</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.44268941879272</v>
+        <v>2.4426896572113</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G90" t="n">
-        <v>2.60387587547302</v>
+        <v>2.6038761138916</v>
       </c>
       <c r="H90" t="n">
         <v>3900</v>
@@ -3008,7 +3008,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H91" t="n">
         <v>2100</v>
@@ -3037,7 +3037,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H92" t="n">
         <v>2700</v>
@@ -3066,7 +3066,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H93" t="n">
         <v>2700</v>
@@ -3414,7 +3414,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="n">
         <v>1800</v>
@@ -3443,7 +3443,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="n">
         <v>2100</v>
@@ -3472,7 +3472,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G111" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H111" t="n">
         <v>10500</v>
@@ -3762,7 +3762,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H118" t="n">
         <v>600</v>
@@ -3820,7 +3820,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078305244446</v>
+        <v>1.91078329086304</v>
       </c>
       <c r="H152" t="n">
         <v>7500</v>
@@ -4806,7 +4806,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4980,7 +4980,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H159" t="n">
         <v>1500</v>
@@ -5009,7 +5009,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H170" t="n">
         <v>300</v>
@@ -5328,7 +5328,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H172" t="n">
         <v>3300</v>
@@ -5386,7 +5386,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H174" t="n">
         <v>2400</v>
@@ -5444,7 +5444,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H179" t="n">
         <v>3600</v>
@@ -5589,7 +5589,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H180" t="n">
         <v>8700</v>
@@ -5618,7 +5618,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G190" t="n">
-        <v>2.21824550628662</v>
+        <v>2.21824526786804</v>
       </c>
       <c r="H190" t="n">
         <v>83700</v>
@@ -5966,7 +5966,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138878822327</v>
+        <v>2.50138902664185</v>
       </c>
       <c r="H193" t="n">
         <v>25500</v>
@@ -6053,7 +6053,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H196" t="n">
         <v>4500</v>
@@ -6082,7 +6082,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G197" t="n">
-        <v>2.32941794395447</v>
+        <v>2.32941818237305</v>
       </c>
       <c r="H197" t="n">
         <v>1800</v>
@@ -6140,7 +6140,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64904022216797</v>
+        <v>2.64903998374939</v>
       </c>
       <c r="H199" t="n">
         <v>54000</v>
@@ -6256,7 +6256,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303117752075</v>
+        <v>2.58303141593933</v>
       </c>
       <c r="H203" t="n">
         <v>2400</v>
@@ -6285,7 +6285,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G204" t="n">
-        <v>2.58650541305542</v>
+        <v>2.58650517463684</v>
       </c>
       <c r="H204" t="n">
         <v>600</v>
@@ -6575,7 +6575,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401761054993</v>
+        <v>2.48401784896851</v>
       </c>
       <c r="H214" t="n">
         <v>1200</v>
@@ -6778,7 +6778,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6807,7 +6807,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H222" t="n">
         <v>16200</v>
@@ -6836,7 +6836,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H227" t="n">
         <v>6300</v>
@@ -6981,7 +6981,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H228" t="n">
         <v>3600</v>
@@ -7010,7 +7010,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H229" t="n">
         <v>9000</v>
@@ -7155,7 +7155,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H234" t="n">
         <v>8100</v>
@@ -7242,7 +7242,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H237" t="n">
         <v>11700</v>
@@ -7271,7 +7271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H238" t="n">
         <v>1200</v>
@@ -7445,7 +7445,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H244" t="n">
         <v>8100</v>
@@ -7503,7 +7503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H250" t="n">
         <v>6300</v>
@@ -7851,7 +7851,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H258" t="n">
         <v>6900</v>
@@ -8083,7 +8083,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H266" t="n">
         <v>1200</v>
@@ -8112,7 +8112,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H267" t="n">
         <v>600</v>
@@ -8315,7 +8315,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H274" t="n">
         <v>6300</v>
@@ -8344,7 +8344,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087159156799</v>
+        <v>2.57087182998657</v>
       </c>
       <c r="H280" t="n">
         <v>2700</v>
@@ -8779,7 +8779,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772533416748</v>
+        <v>2.65772557258606</v>
       </c>
       <c r="H290" t="n">
         <v>35400</v>
@@ -8837,7 +8837,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.74110507965088</v>
+        <v>2.7411048412323</v>
       </c>
       <c r="H292" t="n">
         <v>21600</v>
@@ -8866,7 +8866,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537724494934</v>
+        <v>2.80537700653076</v>
       </c>
       <c r="H293" t="n">
         <v>7200</v>
@@ -8895,7 +8895,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706687927246</v>
+        <v>2.84706664085388</v>
       </c>
       <c r="H294" t="n">
         <v>10500</v>
@@ -8924,7 +8924,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091633796692</v>
+        <v>2.90091609954834</v>
       </c>
       <c r="H295" t="n">
         <v>18300</v>
@@ -8953,7 +8953,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110234260559</v>
+        <v>3.11110210418701</v>
       </c>
       <c r="H296" t="n">
         <v>15600</v>
@@ -9011,7 +9011,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H298" t="n">
         <v>8400</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.50889229774475</v>
+        <v>3.50889253616333</v>
       </c>
       <c r="H299" t="n">
         <v>17700</v>
@@ -9069,7 +9069,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020718574524</v>
+        <v>3.50020694732666</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H301" t="n">
         <v>8400</v>
@@ -9214,7 +9214,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G305" t="n">
-        <v>3.21185255050659</v>
+        <v>3.21185278892517</v>
       </c>
       <c r="H305" t="n">
         <v>300</v>
@@ -9359,7 +9359,7 @@
         <v>3.75</v>
       </c>
       <c r="G310" t="n">
-        <v>3.25701642036438</v>
+        <v>3.25701665878296</v>
       </c>
       <c r="H310" t="n">
         <v>8100</v>
@@ -9620,7 +9620,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480982780457</v>
+        <v>3.28480958938599</v>
       </c>
       <c r="H319" t="n">
         <v>27300</v>
@@ -9765,7 +9765,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218052864075</v>
+        <v>3.30218076705933</v>
       </c>
       <c r="H324" t="n">
         <v>1500</v>
@@ -10113,7 +10113,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170783996582</v>
+        <v>3.70170760154724</v>
       </c>
       <c r="H336" t="n">
         <v>9300</v>
@@ -10142,7 +10142,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339771270752</v>
+        <v>3.7433979511261</v>
       </c>
       <c r="H337" t="n">
         <v>2100</v>
@@ -10171,7 +10171,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987694740295</v>
+        <v>3.7798764705658</v>
       </c>
       <c r="H338" t="n">
         <v>2100</v>
@@ -80009,6 +80009,35 @@
         <v>6000</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895930290222</v>
+        <v>2.24895906448364</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H4" t="n">
         <v>2400</v>
@@ -514,7 +514,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H9" t="n">
         <v>300</v>
@@ -659,7 +659,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H12" t="n">
         <v>2700</v>
@@ -891,7 +891,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H18" t="n">
         <v>600</v>
@@ -920,7 +920,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945889472961</v>
+        <v>2.13945913314819</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0973436832428</v>
+        <v>2.09734392166138</v>
       </c>
       <c r="H27" t="n">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0552282333374</v>
+        <v>2.05522847175598</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1210,7 +1210,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1239,7 +1239,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684385299683</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H31" t="n">
         <v>3600</v>
@@ -1297,7 +1297,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688184738159</v>
+        <v>2.36688208580017</v>
       </c>
       <c r="H36" t="n">
         <v>1500</v>
@@ -1587,7 +1587,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053621292114</v>
+        <v>2.24053597450256</v>
       </c>
       <c r="H42" t="n">
         <v>900</v>
@@ -1616,7 +1616,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315173149109</v>
       </c>
       <c r="H43" t="n">
         <v>1800</v>
@@ -1645,7 +1645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315173149109</v>
       </c>
       <c r="H44" t="n">
         <v>12600</v>
@@ -1674,7 +1674,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315173149109</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315173149109</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H54" t="n">
         <v>5100</v>
@@ -1964,7 +1964,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H55" t="n">
         <v>8400</v>
@@ -1993,7 +1993,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H56" t="n">
         <v>10200</v>
@@ -2022,7 +2022,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H57" t="n">
         <v>300</v>
@@ -2051,7 +2051,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H59" t="n">
         <v>116400</v>
@@ -2196,7 +2196,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745167732239</v>
+        <v>2.10745143890381</v>
       </c>
       <c r="H63" t="n">
         <v>900</v>
@@ -2225,7 +2225,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H64" t="n">
         <v>21600</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H70" t="n">
         <v>1200</v>
@@ -2428,7 +2428,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14788222312927</v>
+        <v>2.14788246154785</v>
       </c>
       <c r="H71" t="n">
         <v>24300</v>
@@ -2457,7 +2457,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.14788222312927</v>
+        <v>2.14788246154785</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="n">
         <v>300</v>
@@ -2515,7 +2515,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820525169373</v>
+        <v>2.1782054901123</v>
       </c>
       <c r="H75" t="n">
         <v>300</v>
@@ -2602,7 +2602,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="n">
         <v>8400</v>
@@ -2631,7 +2631,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35845875740051</v>
+        <v>2.35845899581909</v>
       </c>
       <c r="H78" t="n">
         <v>2700</v>
@@ -2834,7 +2834,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G85" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H85" t="n">
         <v>3900</v>
@@ -2863,7 +2863,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G86" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G87" t="n">
-        <v>2.61429858207703</v>
+        <v>2.61429834365845</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H101" t="n">
         <v>2700</v>
@@ -3327,7 +3327,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="n">
         <v>1800</v>
@@ -3443,7 +3443,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="n">
         <v>2100</v>
@@ -3472,7 +3472,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H112" t="n">
         <v>6600</v>
@@ -3646,7 +3646,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H118" t="n">
         <v>600</v>
@@ -3820,7 +3820,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G125" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H125" t="n">
         <v>1200</v>
@@ -4023,7 +4023,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H126" t="n">
         <v>4500</v>
@@ -4052,7 +4052,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H127" t="n">
         <v>300</v>
@@ -4081,7 +4081,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G140" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H140" t="n">
         <v>2400</v>
@@ -4458,7 +4458,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G142" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078329086304</v>
+        <v>1.91078305244446</v>
       </c>
       <c r="H152" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H159" t="n">
         <v>1500</v>
@@ -5009,7 +5009,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H163" t="n">
         <v>7200</v>
@@ -5125,7 +5125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H165" t="n">
         <v>3600</v>
@@ -5183,7 +5183,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G166" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G167" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998536109924</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H168" t="n">
         <v>9900</v>
@@ -5270,7 +5270,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998536109924</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693371295929</v>
+        <v>1.85693359375</v>
       </c>
       <c r="H174" t="n">
         <v>2400</v>
@@ -5444,7 +5444,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693371295929</v>
+        <v>1.85693359375</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H189" t="n">
         <v>154500</v>
@@ -5908,7 +5908,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H191" t="n">
         <v>45900</v>
@@ -5937,7 +5937,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H192" t="n">
         <v>44100</v>
@@ -5995,7 +5995,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H194" t="n">
         <v>8400</v>
@@ -6053,7 +6053,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H196" t="n">
         <v>4500</v>
@@ -6111,7 +6111,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.43190550804138</v>
+        <v>2.43190574645996</v>
       </c>
       <c r="H198" t="n">
         <v>5100</v>
@@ -6227,7 +6227,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57434558868408</v>
+        <v>2.57434582710266</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6372,7 +6372,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800880432129</v>
+        <v>2.41800904273987</v>
       </c>
       <c r="H207" t="n">
         <v>7800</v>
@@ -6546,7 +6546,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613042831421</v>
+        <v>2.53613018989563</v>
       </c>
       <c r="H213" t="n">
         <v>1200</v>
@@ -6575,7 +6575,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401784896851</v>
+        <v>2.48401761054993</v>
       </c>
       <c r="H214" t="n">
         <v>1200</v>
@@ -6604,7 +6604,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706961631775</v>
+        <v>2.47706937789917</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669439315796</v>
+        <v>2.42669415473938</v>
       </c>
       <c r="H216" t="n">
         <v>3600</v>
@@ -6662,7 +6662,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.43190550804138</v>
+        <v>2.43190574645996</v>
       </c>
       <c r="H217" t="n">
         <v>600</v>
@@ -6691,7 +6691,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.40584969520569</v>
+        <v>2.40584945678711</v>
       </c>
       <c r="H218" t="n">
         <v>1500</v>
@@ -6749,7 +6749,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425407409668</v>
+        <v>2.28425431251526</v>
       </c>
       <c r="H220" t="n">
         <v>21900</v>
@@ -6778,7 +6778,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6807,7 +6807,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H222" t="n">
         <v>16200</v>
@@ -6836,7 +6836,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H227" t="n">
         <v>6300</v>
@@ -6981,7 +6981,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H228" t="n">
         <v>3600</v>
@@ -7010,7 +7010,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H229" t="n">
         <v>9000</v>
@@ -7039,7 +7039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G230" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H230" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G231" t="n">
-        <v>2.20087456703186</v>
+        <v>2.20087432861328</v>
       </c>
       <c r="H231" t="n">
         <v>5700</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H232" t="n">
         <v>1800</v>
@@ -7126,7 +7126,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H233" t="n">
         <v>600</v>
@@ -7155,7 +7155,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H234" t="n">
         <v>8100</v>
@@ -7242,7 +7242,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H237" t="n">
         <v>11700</v>
@@ -7271,7 +7271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H238" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G242" t="n">
-        <v>2.35373711585999</v>
+        <v>2.35373735427856</v>
       </c>
       <c r="H242" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H244" t="n">
         <v>8100</v>
@@ -7474,7 +7474,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>2.35373711585999</v>
+        <v>2.35373735427856</v>
       </c>
       <c r="H245" t="n">
         <v>1500</v>
@@ -7503,7 +7503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H250" t="n">
         <v>6300</v>
@@ -7677,7 +7677,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H252" t="n">
         <v>1200</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H253" t="n">
         <v>2400</v>
@@ -7764,7 +7764,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.38153052330017</v>
+        <v>2.38153076171875</v>
       </c>
       <c r="H255" t="n">
         <v>18000</v>
@@ -7793,7 +7793,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32594394683838</v>
+        <v>2.32594418525696</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G257" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H257" t="n">
         <v>1800</v>
@@ -7851,7 +7851,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H258" t="n">
         <v>6900</v>
@@ -7880,7 +7880,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G259" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H259" t="n">
         <v>1500</v>
@@ -7909,7 +7909,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H260" t="n">
         <v>4800</v>
@@ -7938,7 +7938,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>2.25125002861023</v>
+        <v>2.25124979019165</v>
       </c>
       <c r="H263" t="n">
         <v>8400</v>
@@ -8025,7 +8025,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G264" t="n">
-        <v>2.2251935005188</v>
+        <v>2.22519373893738</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.3242073059082</v>
+        <v>2.32420706748962</v>
       </c>
       <c r="H265" t="n">
         <v>1200</v>
@@ -8083,7 +8083,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H266" t="n">
         <v>1200</v>
@@ -8112,7 +8112,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H267" t="n">
         <v>600</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.35373711585999</v>
+        <v>2.35373735427856</v>
       </c>
       <c r="H273" t="n">
         <v>4200</v>
@@ -8315,7 +8315,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H274" t="n">
         <v>6300</v>
@@ -8344,7 +8344,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847899436951</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8373,7 +8373,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G276" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H276" t="n">
         <v>52500</v>
@@ -8402,7 +8402,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382886886597</v>
+        <v>2.64382863044739</v>
       </c>
       <c r="H277" t="n">
         <v>14700</v>
@@ -8431,7 +8431,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246697425842</v>
+        <v>2.692467212677</v>
       </c>
       <c r="H278" t="n">
         <v>10800</v>
@@ -8460,7 +8460,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>2.61603593826294</v>
+        <v>2.61603569984436</v>
       </c>
       <c r="H279" t="n">
         <v>1800</v>
@@ -8489,7 +8489,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087182998657</v>
+        <v>2.57087159156799</v>
       </c>
       <c r="H280" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H283" t="n">
         <v>900</v>
@@ -8721,7 +8721,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.63166928291321</v>
+        <v>2.63166952133179</v>
       </c>
       <c r="H288" t="n">
         <v>900</v>
@@ -8779,7 +8779,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772557258606</v>
+        <v>2.65772533416748</v>
       </c>
       <c r="H290" t="n">
         <v>35400</v>
@@ -8808,7 +8808,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>2.77063536643982</v>
+        <v>2.7706356048584</v>
       </c>
       <c r="H291" t="n">
         <v>11700</v>
@@ -8866,7 +8866,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537700653076</v>
+        <v>2.80537676811218</v>
       </c>
       <c r="H293" t="n">
         <v>7200</v>
@@ -8924,7 +8924,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091633796692</v>
+        <v>2.90091586112976</v>
       </c>
       <c r="H295" t="n">
         <v>18300</v>
@@ -8953,7 +8953,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110210418701</v>
+        <v>3.11110234260559</v>
       </c>
       <c r="H296" t="n">
         <v>15600</v>
@@ -9011,7 +9011,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.46546530723572</v>
+        <v>3.46546578407288</v>
       </c>
       <c r="H298" t="n">
         <v>8400</v>
@@ -9069,7 +9069,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020718574524</v>
+        <v>3.50020742416382</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.46546530723572</v>
+        <v>3.46546578407288</v>
       </c>
       <c r="H301" t="n">
         <v>8400</v>
@@ -9127,7 +9127,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124110221863</v>
+        <v>3.36124086380005</v>
       </c>
       <c r="H302" t="n">
         <v>18000</v>
@@ -9156,7 +9156,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H303" t="n">
         <v>14700</v>
@@ -9243,7 +9243,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H306" t="n">
         <v>27300</v>
@@ -9330,7 +9330,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G309" t="n">
-        <v>3.13194680213928</v>
+        <v>3.13194704055786</v>
       </c>
       <c r="H309" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H311" t="n">
         <v>900</v>
@@ -9446,7 +9446,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>3.23964595794678</v>
+        <v>3.2396457195282</v>
       </c>
       <c r="H313" t="n">
         <v>3300</v>
@@ -9504,7 +9504,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H316" t="n">
         <v>2700</v>
@@ -9562,7 +9562,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>3.37861204147339</v>
+        <v>3.37861180305481</v>
       </c>
       <c r="H318" t="n">
         <v>7200</v>
@@ -9649,7 +9649,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34386992454529</v>
+        <v>3.34387040138245</v>
       </c>
       <c r="H320" t="n">
         <v>6300</v>
@@ -9707,7 +9707,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H322" t="n">
         <v>12300</v>
@@ -9736,7 +9736,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H323" t="n">
         <v>300</v>
@@ -9765,7 +9765,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218052864075</v>
+        <v>3.30218076705933</v>
       </c>
       <c r="H324" t="n">
         <v>1500</v>
@@ -9939,7 +9939,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H330" t="n">
         <v>15000</v>
@@ -9997,7 +9997,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588777542114</v>
+        <v>3.47588801383972</v>
       </c>
       <c r="H332" t="n">
         <v>900</v>
@@ -10055,7 +10055,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706116676331</v>
+        <v>3.58706092834473</v>
       </c>
       <c r="H334" t="n">
         <v>2700</v>
@@ -10142,7 +10142,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339747428894</v>
+        <v>3.74339771270752</v>
       </c>
       <c r="H337" t="n">
         <v>2100</v>
@@ -10171,7 +10171,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987623214722</v>
+        <v>3.77987670898438</v>
       </c>
       <c r="H338" t="n">
         <v>2100</v>
@@ -10200,7 +10200,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G339" t="n">
-        <v>3.78335046768188</v>
+        <v>3.78335022926331</v>
       </c>
       <c r="H339" t="n">
         <v>5400</v>
@@ -10258,7 +10258,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G341" t="n">
-        <v>3.90668296813965</v>
+        <v>3.90668272972107</v>
       </c>
       <c r="H341" t="n">
         <v>600</v>
@@ -10432,7 +10432,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.27162313461304</v>
+        <v>4.27162265777588</v>
       </c>
       <c r="H347" t="n">
         <v>2100</v>
@@ -10461,7 +10461,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H348" t="n">
         <v>2100</v>
@@ -10548,7 +10548,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H351" t="n">
         <v>900</v>
@@ -10577,7 +10577,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H352" t="n">
         <v>4200</v>
@@ -10809,7 +10809,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>4.44517946243286</v>
+        <v>4.44517993927002</v>
       </c>
       <c r="H360" t="n">
         <v>4800</v>
@@ -10925,7 +10925,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H364" t="n">
         <v>300</v>
@@ -10954,7 +10954,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G365" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H365" t="n">
         <v>600</v>
@@ -10983,7 +10983,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G368" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H368" t="n">
         <v>5100</v>
@@ -11070,7 +11070,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G369" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H374" t="n">
         <v>8400</v>
@@ -11360,7 +11360,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>4.18838691711426</v>
+        <v>4.1883864402771</v>
       </c>
       <c r="H379" t="n">
         <v>600</v>
@@ -11389,7 +11389,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>4.18838691711426</v>
+        <v>4.1883864402771</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>4.18838691711426</v>
+        <v>4.1883864402771</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>4.75</v>
       </c>
       <c r="G387" t="n">
-        <v>4.20609617233276</v>
+        <v>4.20609664916992</v>
       </c>
       <c r="H387" t="n">
         <v>1800</v>
@@ -11708,7 +11708,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H391" t="n">
         <v>2100</v>
@@ -11795,7 +11795,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G394" t="n">
-        <v>4.39027976989746</v>
+        <v>4.3902792930603</v>
       </c>
       <c r="H394" t="n">
         <v>2400</v>
@@ -11824,7 +11824,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H395" t="n">
         <v>2700</v>
@@ -11853,7 +11853,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G396" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H396" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G406" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H406" t="n">
         <v>2700</v>
@@ -12172,7 +12172,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H407" t="n">
         <v>2100</v>
@@ -12201,7 +12201,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G408" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H408" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H410" t="n">
         <v>3900</v>
@@ -12288,7 +12288,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G413" t="n">
-        <v>4.04316520690918</v>
+        <v>4.04316568374634</v>
       </c>
       <c r="H413" t="n">
         <v>600</v>
@@ -12375,7 +12375,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H414" t="n">
         <v>1200</v>
@@ -12433,7 +12433,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G416" t="n">
-        <v>3.9758677482605</v>
+        <v>3.97586822509766</v>
       </c>
       <c r="H416" t="n">
         <v>900</v>
@@ -12462,7 +12462,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G417" t="n">
-        <v>3.9758677482605</v>
+        <v>3.97586822509766</v>
       </c>
       <c r="H417" t="n">
         <v>600</v>
@@ -12491,7 +12491,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G418" t="n">
-        <v>3.9758677482605</v>
+        <v>3.97586822509766</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G422" t="n">
-        <v>3.94576120376587</v>
+        <v>3.94576096534729</v>
       </c>
       <c r="H422" t="n">
         <v>7500</v>
@@ -12636,7 +12636,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H423" t="n">
         <v>3900</v>
@@ -12665,7 +12665,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H424" t="n">
         <v>6900</v>
@@ -12781,7 +12781,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H428" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H430" t="n">
         <v>2700</v>
@@ -12868,7 +12868,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H432" t="n">
         <v>1200</v>
@@ -12926,7 +12926,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H434" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H435" t="n">
         <v>1200</v>
@@ -13013,7 +13013,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H438" t="n">
         <v>1800</v>
@@ -13100,7 +13100,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H439" t="n">
         <v>1200</v>
@@ -13129,7 +13129,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G444" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H444" t="n">
         <v>2100</v>
@@ -13303,7 +13303,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G446" t="n">
-        <v>4.3725700378418</v>
+        <v>4.37256956100464</v>
       </c>
       <c r="H446" t="n">
         <v>4200</v>
@@ -13361,7 +13361,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G448" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H448" t="n">
         <v>14700</v>
@@ -13390,7 +13390,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H449" t="n">
         <v>6900</v>
@@ -13535,7 +13535,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H454" t="n">
         <v>600</v>
@@ -13564,7 +13564,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G455" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H455" t="n">
         <v>1200</v>
@@ -13593,7 +13593,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G456" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H456" t="n">
         <v>19800</v>
@@ -13709,7 +13709,7 @@
         <v>4.75</v>
       </c>
       <c r="G460" t="n">
-        <v>4.20609617233276</v>
+        <v>4.20609664916992</v>
       </c>
       <c r="H460" t="n">
         <v>3000</v>
@@ -13738,7 +13738,7 @@
         <v>4.75</v>
       </c>
       <c r="G461" t="n">
-        <v>4.20609617233276</v>
+        <v>4.20609664916992</v>
       </c>
       <c r="H461" t="n">
         <v>7800</v>
@@ -13825,7 +13825,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786762237549</v>
+        <v>4.20786714553833</v>
       </c>
       <c r="H464" t="n">
         <v>10200</v>
@@ -13883,7 +13883,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H466" t="n">
         <v>4200</v>
@@ -13912,7 +13912,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G467" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G469" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H469" t="n">
         <v>6300</v>
@@ -13999,7 +13999,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G470" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H471" t="n">
         <v>12300</v>
@@ -14115,7 +14115,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H474" t="n">
         <v>4200</v>
@@ -14376,7 +14376,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G483" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H483" t="n">
         <v>300</v>
@@ -14405,7 +14405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G485" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H485" t="n">
         <v>900</v>
@@ -14463,7 +14463,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G486" t="n">
-        <v>4.07858562469482</v>
+        <v>4.07858514785767</v>
       </c>
       <c r="H486" t="n">
         <v>6900</v>
@@ -14666,7 +14666,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G493" t="n">
-        <v>4.17953157424927</v>
+        <v>4.17953205108643</v>
       </c>
       <c r="H493" t="n">
         <v>6600</v>
@@ -14724,7 +14724,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G495" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H495" t="n">
         <v>16500</v>
@@ -14782,7 +14782,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H497" t="n">
         <v>600</v>
@@ -14811,7 +14811,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G500" t="n">
-        <v>4.03431129455566</v>
+        <v>4.03431081771851</v>
       </c>
       <c r="H500" t="n">
         <v>10800</v>
@@ -14898,7 +14898,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H501" t="n">
         <v>6300</v>
@@ -14927,7 +14927,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G502" t="n">
-        <v>3.95107436180115</v>
+        <v>3.95107388496399</v>
       </c>
       <c r="H502" t="n">
         <v>3300</v>
@@ -15043,7 +15043,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.8253345489502</v>
+        <v>3.82533431053162</v>
       </c>
       <c r="H506" t="n">
         <v>2700</v>
@@ -15072,7 +15072,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H507" t="n">
         <v>5100</v>
@@ -15101,7 +15101,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H515" t="n">
         <v>1200</v>
@@ -15333,7 +15333,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H516" t="n">
         <v>900</v>
@@ -15478,7 +15478,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H521" t="n">
         <v>1500</v>
@@ -15507,7 +15507,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H522" t="n">
         <v>4200</v>
@@ -15536,7 +15536,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G524" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H524" t="n">
         <v>600</v>
@@ -15594,7 +15594,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G529" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H529" t="n">
         <v>26100</v>
@@ -15739,7 +15739,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G531" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H534" t="n">
         <v>6600</v>
@@ -15913,7 +15913,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H536" t="n">
         <v>300</v>
@@ -15942,7 +15942,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G537" t="n">
-        <v>3.84304428100586</v>
+        <v>3.8430438041687</v>
       </c>
       <c r="H537" t="n">
         <v>300</v>
@@ -16000,7 +16000,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H539" t="n">
         <v>300</v>
@@ -16116,7 +16116,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H548" t="n">
         <v>4200</v>
@@ -16464,7 +16464,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H555" t="n">
         <v>8100</v>
@@ -16609,7 +16609,7 @@
         <v>4.5</v>
       </c>
       <c r="G560" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H560" t="n">
         <v>2100</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H565" t="n">
         <v>4500</v>
@@ -16783,7 +16783,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H566" t="n">
         <v>4200</v>
@@ -16812,7 +16812,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G567" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H567" t="n">
         <v>4500</v>
@@ -16841,7 +16841,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G568" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H568" t="n">
         <v>3600</v>
@@ -16986,7 +16986,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H573" t="n">
         <v>49500</v>
@@ -17044,7 +17044,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H575" t="n">
         <v>18900</v>
@@ -17073,7 +17073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>4.60456895828247</v>
+        <v>4.60456848144531</v>
       </c>
       <c r="H576" t="n">
         <v>8100</v>
@@ -17276,7 +17276,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H583" t="n">
         <v>6600</v>
@@ -17334,7 +17334,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H585" t="n">
         <v>5100</v>
@@ -17363,7 +17363,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H586" t="n">
         <v>300</v>
@@ -17392,7 +17392,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H587" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H591" t="n">
         <v>2100</v>
@@ -17595,7 +17595,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G594" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H594" t="n">
         <v>300</v>
@@ -17624,7 +17624,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H595" t="n">
         <v>3000</v>
@@ -17653,7 +17653,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H596" t="n">
         <v>1200</v>
@@ -17827,7 +17827,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H602" t="n">
         <v>21300</v>
@@ -17885,7 +17885,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H604" t="n">
         <v>12300</v>
@@ -17943,7 +17943,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H606" t="n">
         <v>4800</v>
@@ -17972,7 +17972,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H607" t="n">
         <v>1500</v>
@@ -18001,7 +18001,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G608" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H608" t="n">
         <v>4500</v>
@@ -18030,7 +18030,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G610" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H610" t="n">
         <v>600</v>
@@ -18088,7 +18088,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G611" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -18117,7 +18117,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G612" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H612" t="n">
         <v>900</v>
@@ -18407,7 +18407,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.51601934432983</v>
+        <v>4.51601982116699</v>
       </c>
       <c r="H622" t="n">
         <v>10500</v>
@@ -18523,7 +18523,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H626" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G630" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H630" t="n">
         <v>6300</v>
@@ -18668,7 +18668,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H631" t="n">
         <v>0</v>
@@ -18697,7 +18697,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>4.40975999832153</v>
+        <v>4.40976047515869</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G635" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H635" t="n">
         <v>2700</v>
@@ -18813,7 +18813,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G636" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G637" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H642" t="n">
         <v>9900</v>
@@ -19016,7 +19016,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19248,7 +19248,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G651" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H651" t="n">
         <v>300</v>
@@ -19277,7 +19277,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H652" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G656" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H656" t="n">
         <v>900</v>
@@ -19422,7 +19422,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G657" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19538,7 +19538,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G662" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G664" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G665" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19712,7 +19712,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G667" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H667" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -20234,7 +20234,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.87846374511719</v>
+        <v>3.87846398353577</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20263,7 +20263,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H686" t="n">
         <v>5700</v>
@@ -20292,7 +20292,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -20408,7 +20408,7 @@
         <v>4.5</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H691" t="n">
         <v>1800</v>
@@ -20524,7 +20524,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G695" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H695" t="n">
         <v>3000</v>
@@ -20582,7 +20582,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H697" t="n">
         <v>3300</v>
@@ -20611,7 +20611,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>4.39205026626587</v>
+        <v>4.39204978942871</v>
       </c>
       <c r="H702" t="n">
         <v>300</v>
@@ -20756,7 +20756,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H703" t="n">
         <v>5100</v>
@@ -20785,7 +20785,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G704" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H704" t="n">
         <v>2100</v>
@@ -20814,7 +20814,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H705" t="n">
         <v>3000</v>
@@ -20843,7 +20843,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H706" t="n">
         <v>3300</v>
@@ -21017,7 +21017,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G712" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H712" t="n">
         <v>600</v>
@@ -21220,7 +21220,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G719" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H719" t="n">
         <v>600</v>
@@ -21307,7 +21307,7 @@
         <v>4.5</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H722" t="n">
         <v>900</v>
@@ -21336,7 +21336,7 @@
         <v>4.5</v>
       </c>
       <c r="G723" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>4.5</v>
       </c>
       <c r="G724" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H738" t="n">
         <v>900</v>
@@ -21800,7 +21800,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G739" t="n">
-        <v>4.17953157424927</v>
+        <v>4.17953205108643</v>
       </c>
       <c r="H739" t="n">
         <v>3600</v>
@@ -22235,7 +22235,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G754" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H754" t="n">
         <v>300</v>
@@ -22264,7 +22264,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H755" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G757" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G758" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G759" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G760" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G761" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22467,7 +22467,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G762" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>4.5</v>
       </c>
       <c r="G773" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H773" t="n">
         <v>1200</v>
@@ -22844,7 +22844,7 @@
         <v>4.5</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H775" t="n">
         <v>600</v>
@@ -22873,7 +22873,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H776" t="n">
         <v>6900</v>
@@ -22902,7 +22902,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -22931,7 +22931,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -22960,7 +22960,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388344764709</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G781" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H781" t="n">
         <v>600</v>
@@ -23047,7 +23047,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H782" t="n">
         <v>0</v>
@@ -23076,7 +23076,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G783" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23366,7 +23366,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H793" t="n">
         <v>21300</v>
@@ -23511,7 +23511,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H798" t="n">
         <v>600</v>
@@ -23540,7 +23540,7 @@
         <v>4.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472309112549</v>
       </c>
       <c r="H799" t="n">
         <v>3600</v>
@@ -23598,7 +23598,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G801" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H801" t="n">
         <v>600</v>
@@ -23772,7 +23772,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H807" t="n">
         <v>2700</v>
@@ -23801,7 +23801,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H809" t="n">
         <v>600</v>
@@ -23859,7 +23859,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H811" t="n">
         <v>0</v>
@@ -24149,7 +24149,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G820" t="n">
-        <v>4.17953157424927</v>
+        <v>4.17953205108643</v>
       </c>
       <c r="H820" t="n">
         <v>2100</v>
@@ -24178,7 +24178,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G821" t="n">
-        <v>4.17953157424927</v>
+        <v>4.17953205108643</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G822" t="n">
-        <v>4.17953157424927</v>
+        <v>4.17953205108643</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H823" t="n">
         <v>1200</v>
@@ -24265,7 +24265,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G824" t="n">
-        <v>4.26808166503906</v>
+        <v>4.2680811882019</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G830" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H830" t="n">
         <v>1200</v>
@@ -24468,7 +24468,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H831" t="n">
         <v>6000</v>
@@ -24497,7 +24497,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H833" t="n">
         <v>2700</v>
@@ -24642,7 +24642,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G837" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H837" t="n">
         <v>3900</v>
@@ -24671,7 +24671,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G838" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G843" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H843" t="n">
         <v>900</v>
@@ -24903,7 +24903,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G846" t="n">
-        <v>4.32121086120605</v>
+        <v>4.3212103843689</v>
       </c>
       <c r="H846" t="n">
         <v>300</v>
@@ -24990,7 +24990,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H849" t="n">
         <v>2700</v>
@@ -25019,7 +25019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H851" t="n">
         <v>3000</v>
@@ -25077,7 +25077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -25164,7 +25164,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H855" t="n">
         <v>6300</v>
@@ -25193,7 +25193,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H856" t="n">
         <v>300</v>
@@ -25222,7 +25222,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G857" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G858" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G859" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H860" t="n">
         <v>1800</v>
@@ -25338,7 +25338,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G861" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H861" t="n">
         <v>600</v>
@@ -25860,7 +25860,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G879" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H879" t="n">
         <v>1800</v>
@@ -25889,7 +25889,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G880" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G881" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G883" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H883" t="n">
         <v>10200</v>
@@ -26556,7 +26556,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H903" t="n">
         <v>600</v>
@@ -26585,7 +26585,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H904" t="n">
         <v>2700</v>
@@ -26672,7 +26672,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G907" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H907" t="n">
         <v>600</v>
@@ -26730,7 +26730,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H909" t="n">
         <v>300</v>
@@ -26759,7 +26759,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H915" t="n">
         <v>3300</v>
@@ -27078,7 +27078,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>4.40378189086914</v>
+        <v>4.40378141403198</v>
       </c>
       <c r="H921" t="n">
         <v>300</v>
@@ -27890,7 +27890,7 @@
         <v>5</v>
       </c>
       <c r="G949" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H949" t="n">
         <v>900</v>
@@ -27919,7 +27919,7 @@
         <v>5</v>
       </c>
       <c r="G950" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -27948,7 +27948,7 @@
         <v>5</v>
       </c>
       <c r="G951" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>5</v>
       </c>
       <c r="G952" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -28006,7 +28006,7 @@
         <v>5</v>
       </c>
       <c r="G953" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28035,7 +28035,7 @@
         <v>5</v>
       </c>
       <c r="G954" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H954" t="n">
         <v>9000</v>
@@ -28644,7 +28644,7 @@
         <v>5</v>
       </c>
       <c r="G975" t="n">
-        <v>4.51207113265991</v>
+        <v>4.51207160949707</v>
       </c>
       <c r="H975" t="n">
         <v>900</v>
@@ -28818,7 +28818,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H981" t="n">
         <v>3300</v>
@@ -28847,7 +28847,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H982" t="n">
         <v>2100</v>
@@ -28876,7 +28876,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24134731292725</v>
+        <v>4.24134683609009</v>
       </c>
       <c r="H983" t="n">
         <v>13200</v>
@@ -28905,7 +28905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H984" t="n">
         <v>1200</v>
@@ -29079,7 +29079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H990" t="n">
         <v>300</v>
@@ -29108,7 +29108,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G991" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.1511058807373</v>
+        <v>4.15110540390015</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -29572,7 +29572,7 @@
         <v>4.5</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.06086397171021</v>
+        <v>4.06086444854736</v>
       </c>
       <c r="H1007" t="n">
         <v>3600</v>
@@ -29601,7 +29601,7 @@
         <v>4.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.06086397171021</v>
+        <v>4.06086444854736</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -30094,7 +30094,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.80818796157837</v>
+        <v>3.80818819999695</v>
       </c>
       <c r="H1025" t="n">
         <v>600</v>
@@ -30123,7 +30123,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.80818796157837</v>
+        <v>3.80818819999695</v>
       </c>
       <c r="H1026" t="n">
         <v>3300</v>
@@ -30181,7 +30181,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.80818796157837</v>
+        <v>3.80818819999695</v>
       </c>
       <c r="H1028" t="n">
         <v>6900</v>
@@ -30210,7 +30210,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1029" t="n">
         <v>300</v>
@@ -30471,7 +30471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1038" t="n">
         <v>1500</v>
@@ -30645,7 +30645,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1044" t="n">
         <v>4500</v>
@@ -30674,7 +30674,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1046" t="n">
         <v>2700</v>
@@ -30732,7 +30732,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30790,7 +30790,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.79013967514038</v>
+        <v>3.79013991355896</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -31051,7 +31051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.33893275260925</v>
+        <v>3.33893299102783</v>
       </c>
       <c r="H1058" t="n">
         <v>300</v>
@@ -31080,7 +31080,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.46527099609375</v>
+        <v>3.46527075767517</v>
       </c>
       <c r="H1059" t="n">
         <v>14400</v>
@@ -31109,7 +31109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.46527099609375</v>
+        <v>3.46527075767517</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.80818796157837</v>
+        <v>3.80818819999695</v>
       </c>
       <c r="H1064" t="n">
         <v>3300</v>
@@ -31254,7 +31254,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.64575386047363</v>
+        <v>3.64575362205505</v>
       </c>
       <c r="H1065" t="n">
         <v>900</v>
@@ -31892,7 +31892,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.33893275260925</v>
+        <v>3.33893299102783</v>
       </c>
       <c r="H1087" t="n">
         <v>900</v>
@@ -32124,7 +32124,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.99601531028748</v>
+        <v>2.99601554870605</v>
       </c>
       <c r="H1095" t="n">
         <v>1800</v>
@@ -32153,7 +32153,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.99601531028748</v>
+        <v>2.99601554870605</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -32182,7 +32182,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.99601531028748</v>
+        <v>2.99601554870605</v>
       </c>
       <c r="H1097" t="n">
         <v>0</v>
@@ -32733,7 +32733,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1116" t="n">
         <v>16800</v>
@@ -32936,7 +32936,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1123" t="n">
         <v>1200</v>
@@ -32965,7 +32965,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1124" t="n">
         <v>6000</v>
@@ -32994,7 +32994,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.63504958152771</v>
+        <v>2.63504981994629</v>
       </c>
       <c r="H1125" t="n">
         <v>20400</v>
@@ -33835,7 +33835,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1154" t="n">
         <v>600</v>
@@ -33864,7 +33864,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1155" t="n">
         <v>0</v>
@@ -34038,7 +34038,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1161" t="n">
         <v>1800</v>
@@ -34067,7 +34067,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1162" t="n">
         <v>0</v>
@@ -34096,7 +34096,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1163" t="n">
         <v>0</v>
@@ -34125,7 +34125,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1164" t="n">
         <v>0</v>
@@ -34154,7 +34154,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1165" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1190" t="n">
         <v>900</v>
@@ -34908,7 +34908,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1192" t="n">
         <v>0</v>
@@ -34966,7 +34966,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1193" t="n">
         <v>0</v>
@@ -34995,7 +34995,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1194" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1197" t="n">
         <v>600</v>
@@ -35111,7 +35111,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1198" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1199" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1203" t="n">
         <v>2100</v>
@@ -35285,7 +35285,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27408409118652</v>
+        <v>2.27408385276794</v>
       </c>
       <c r="H1204" t="n">
         <v>300</v>
@@ -35314,7 +35314,7 @@
         <v>2.5</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1205" t="n">
         <v>300</v>
@@ -35343,7 +35343,7 @@
         <v>2.5</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1206" t="n">
         <v>0</v>
@@ -35372,7 +35372,7 @@
         <v>2.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1207" t="n">
         <v>0</v>
@@ -35401,7 +35401,7 @@
         <v>2.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1208" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.07555294036865</v>
+        <v>2.07555270195007</v>
       </c>
       <c r="H1210" t="n">
         <v>900</v>
@@ -35546,7 +35546,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1213" t="n">
         <v>16200</v>
@@ -35604,7 +35604,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1215" t="n">
         <v>3000</v>
@@ -35633,7 +35633,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1216" t="n">
         <v>3000</v>
@@ -35662,7 +35662,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1217" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1218" t="n">
         <v>0</v>
@@ -35720,7 +35720,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1219" t="n">
         <v>0</v>
@@ -35749,7 +35749,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1220" t="n">
         <v>0</v>
@@ -35923,7 +35923,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.82287693023682</v>
+        <v>1.82287681102753</v>
       </c>
       <c r="H1226" t="n">
         <v>3300</v>
@@ -35952,7 +35952,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.82287693023682</v>
+        <v>1.82287681102753</v>
       </c>
       <c r="H1227" t="n">
         <v>2100</v>
@@ -36126,7 +36126,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1233" t="n">
         <v>2700</v>
@@ -36155,7 +36155,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.96726310253143</v>
+        <v>1.96726334095001</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.07555294036865</v>
+        <v>2.07555270195007</v>
       </c>
       <c r="H1236" t="n">
         <v>300</v>
@@ -36474,7 +36474,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.09360098838806</v>
+        <v>2.09360122680664</v>
       </c>
       <c r="H1245" t="n">
         <v>2700</v>
@@ -36677,7 +36677,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.12969756126404</v>
+        <v>2.12969779968262</v>
       </c>
       <c r="H1252" t="n">
         <v>600</v>
@@ -36706,7 +36706,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1253" t="n">
         <v>1500</v>
@@ -36735,7 +36735,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1254" t="n">
         <v>300</v>
@@ -36764,7 +36764,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1255" t="n">
         <v>0</v>
@@ -36822,7 +36822,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.20189094543457</v>
+        <v>2.20189070701599</v>
       </c>
       <c r="H1257" t="n">
         <v>300</v>
@@ -36851,7 +36851,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.20189094543457</v>
+        <v>2.20189070701599</v>
       </c>
       <c r="H1258" t="n">
         <v>0</v>
@@ -36880,7 +36880,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1259" t="n">
         <v>1500</v>
@@ -36909,7 +36909,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1260" t="n">
         <v>0</v>
@@ -36938,7 +36938,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1261" t="n">
         <v>0</v>
@@ -36967,7 +36967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1262" t="n">
         <v>0</v>
@@ -36996,7 +36996,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1263" t="n">
         <v>0</v>
@@ -37025,7 +37025,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.12969756126404</v>
+        <v>2.12969779968262</v>
       </c>
       <c r="H1264" t="n">
         <v>600</v>
@@ -37141,7 +37141,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.12969756126404</v>
+        <v>2.12969779968262</v>
       </c>
       <c r="H1268" t="n">
         <v>1500</v>
@@ -37170,7 +37170,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.12969756126404</v>
+        <v>2.12969779968262</v>
       </c>
       <c r="H1269" t="n">
         <v>0</v>
@@ -37199,7 +37199,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.12969756126404</v>
+        <v>2.12969779968262</v>
       </c>
       <c r="H1270" t="n">
         <v>0</v>
@@ -37228,7 +37228,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.20189094543457</v>
+        <v>2.20189070701599</v>
       </c>
       <c r="H1271" t="n">
         <v>7500</v>
@@ -37286,7 +37286,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1273" t="n">
         <v>900</v>
@@ -37315,7 +37315,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.20189094543457</v>
+        <v>2.20189070701599</v>
       </c>
       <c r="H1274" t="n">
         <v>900</v>
@@ -37402,7 +37402,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1277" t="n">
         <v>600</v>
@@ -37605,7 +37605,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.63504958152771</v>
+        <v>2.63504981994629</v>
       </c>
       <c r="H1284" t="n">
         <v>55200</v>
@@ -37750,7 +37750,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.27408409118652</v>
+        <v>2.27408385276794</v>
       </c>
       <c r="H1289" t="n">
         <v>9300</v>
@@ -37779,7 +37779,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1290" t="n">
         <v>9300</v>
@@ -37808,7 +37808,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.20189094543457</v>
+        <v>2.20189070701599</v>
       </c>
       <c r="H1291" t="n">
         <v>7800</v>
@@ -37866,7 +37866,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.27408409118652</v>
+        <v>2.27408385276794</v>
       </c>
       <c r="H1293" t="n">
         <v>25800</v>
@@ -38040,7 +38040,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.36432528495789</v>
+        <v>2.36432552337646</v>
       </c>
       <c r="H1299" t="n">
         <v>4500</v>
@@ -38069,7 +38069,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.36432528495789</v>
+        <v>2.36432552337646</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.36432528495789</v>
+        <v>2.36432552337646</v>
       </c>
       <c r="H1301" t="n">
         <v>300</v>
@@ -38127,7 +38127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1302" t="n">
         <v>4200</v>
@@ -38156,7 +38156,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1303" t="n">
         <v>0</v>
@@ -38185,7 +38185,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1304" t="n">
         <v>0</v>
@@ -38214,7 +38214,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1305" t="n">
         <v>300</v>
@@ -38243,7 +38243,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1306" t="n">
         <v>0</v>
@@ -38272,7 +38272,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1307" t="n">
         <v>1500</v>
@@ -38330,7 +38330,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1309" t="n">
         <v>6900</v>
@@ -38359,7 +38359,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1310" t="n">
         <v>1200</v>
@@ -38388,7 +38388,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1311" t="n">
         <v>0</v>
@@ -38504,7 +38504,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1315" t="n">
         <v>1800</v>
@@ -38533,7 +38533,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1316" t="n">
         <v>0</v>
@@ -39113,7 +39113,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1336" t="n">
         <v>300</v>
@@ -39142,7 +39142,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1337" t="n">
         <v>0</v>
@@ -39171,7 +39171,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1338" t="n">
         <v>0</v>
@@ -39200,7 +39200,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1339" t="n">
         <v>0</v>
@@ -39345,7 +39345,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1344" t="n">
         <v>3600</v>
@@ -39374,7 +39374,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1345" t="n">
         <v>6000</v>
@@ -39403,7 +39403,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1346" t="n">
         <v>0</v>
@@ -39490,7 +39490,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1349" t="n">
         <v>15300</v>
@@ -39548,7 +39548,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1351" t="n">
         <v>3600</v>
@@ -39780,7 +39780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.32822871208191</v>
+        <v>2.32822895050049</v>
       </c>
       <c r="H1359" t="n">
         <v>17400</v>
@@ -39809,7 +39809,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1360" t="n">
         <v>3000</v>
@@ -39838,7 +39838,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1361" t="n">
         <v>0</v>
@@ -39925,7 +39925,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1364" t="n">
         <v>300</v>
@@ -39954,7 +39954,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1365" t="n">
         <v>3600</v>
@@ -40418,7 +40418,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1381" t="n">
         <v>5100</v>
@@ -40534,7 +40534,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.63504958152771</v>
+        <v>2.63504981994629</v>
       </c>
       <c r="H1385" t="n">
         <v>19800</v>
@@ -40563,7 +40563,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.63504958152771</v>
+        <v>2.63504981994629</v>
       </c>
       <c r="H1386" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1390" t="n">
         <v>4800</v>
@@ -40737,7 +40737,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.99601531028748</v>
+        <v>2.99601554870605</v>
       </c>
       <c r="H1392" t="n">
         <v>62400</v>
@@ -40766,7 +40766,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.01406383514404</v>
+        <v>3.01406359672546</v>
       </c>
       <c r="H1393" t="n">
         <v>62100</v>
@@ -40795,7 +40795,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1394" t="n">
         <v>21000</v>
@@ -40824,7 +40824,7 @@
         <v>3.5</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1395" t="n">
         <v>27600</v>
@@ -40911,7 +40911,7 @@
         <v>3.5</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1398" t="n">
         <v>7200</v>
@@ -40998,7 +40998,7 @@
         <v>3.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1401" t="n">
         <v>12900</v>
@@ -41056,7 +41056,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1403" t="n">
         <v>4200</v>
@@ -41085,7 +41085,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1404" t="n">
         <v>1800</v>
@@ -41114,7 +41114,7 @@
         <v>3.5</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1405" t="n">
         <v>8700</v>
@@ -41143,7 +41143,7 @@
         <v>3.5</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1406" t="n">
         <v>2700</v>
@@ -41201,7 +41201,7 @@
         <v>3.5</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1408" t="n">
         <v>2100</v>
@@ -41259,7 +41259,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.17649841308594</v>
+        <v>3.17649817466736</v>
       </c>
       <c r="H1410" t="n">
         <v>12300</v>
@@ -41317,7 +41317,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.17649841308594</v>
+        <v>3.17649817466736</v>
       </c>
       <c r="H1412" t="n">
         <v>3000</v>
@@ -41346,7 +41346,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.17649841308594</v>
+        <v>3.17649817466736</v>
       </c>
       <c r="H1413" t="n">
         <v>0</v>
@@ -41404,7 +41404,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.17649841308594</v>
+        <v>3.17649817466736</v>
       </c>
       <c r="H1415" t="n">
         <v>300</v>
@@ -41433,7 +41433,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1416" t="n">
         <v>1500</v>
@@ -41462,7 +41462,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1417" t="n">
         <v>0</v>
@@ -41491,7 +41491,7 @@
         <v>3.5</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.15844988822937</v>
+        <v>3.15845012664795</v>
       </c>
       <c r="H1418" t="n">
         <v>3300</v>
@@ -41520,7 +41520,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1419" t="n">
         <v>600</v>
@@ -41549,7 +41549,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1420" t="n">
         <v>0</v>
@@ -41578,7 +41578,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1421" t="n">
         <v>0</v>
@@ -41607,7 +41607,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1422" t="n">
         <v>600</v>
@@ -41636,7 +41636,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.19454646110535</v>
+        <v>3.19454669952393</v>
       </c>
       <c r="H1423" t="n">
         <v>0</v>
@@ -41839,7 +41839,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.97796726226807</v>
+        <v>2.97796702384949</v>
       </c>
       <c r="H1430" t="n">
         <v>900</v>
@@ -41868,7 +41868,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.97796726226807</v>
+        <v>2.97796702384949</v>
       </c>
       <c r="H1431" t="n">
         <v>0</v>
@@ -41897,7 +41897,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.92382216453552</v>
+        <v>2.9238224029541</v>
       </c>
       <c r="H1432" t="n">
         <v>3000</v>
@@ -41926,7 +41926,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.92382216453552</v>
+        <v>2.9238224029541</v>
       </c>
       <c r="H1433" t="n">
         <v>0</v>
@@ -41955,7 +41955,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.94187068939209</v>
+        <v>2.94187045097351</v>
       </c>
       <c r="H1434" t="n">
         <v>300</v>
@@ -41984,7 +41984,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.97796726226807</v>
+        <v>2.97796702384949</v>
       </c>
       <c r="H1435" t="n">
         <v>300</v>
@@ -42129,7 +42129,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.01406383514404</v>
+        <v>3.01406359672546</v>
       </c>
       <c r="H1440" t="n">
         <v>14100</v>
@@ -42187,7 +42187,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.92382216453552</v>
+        <v>2.9238224029541</v>
       </c>
       <c r="H1442" t="n">
         <v>54900</v>
@@ -42216,7 +42216,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.92382216453552</v>
+        <v>2.9238224029541</v>
       </c>
       <c r="H1443" t="n">
         <v>0</v>
@@ -42390,7 +42390,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.92382216453552</v>
+        <v>2.9238224029541</v>
       </c>
       <c r="H1449" t="n">
         <v>22500</v>
@@ -42419,7 +42419,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.9599187374115</v>
+        <v>2.95991897583008</v>
       </c>
       <c r="H1450" t="n">
         <v>25200</v>
@@ -42651,7 +42651,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.9599187374115</v>
+        <v>2.95991897583008</v>
       </c>
       <c r="H1458" t="n">
         <v>17400</v>
@@ -42680,7 +42680,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.9599187374115</v>
+        <v>2.95991897583008</v>
       </c>
       <c r="H1459" t="n">
         <v>0</v>
@@ -42709,7 +42709,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.9599187374115</v>
+        <v>2.95991897583008</v>
       </c>
       <c r="H1460" t="n">
         <v>3600</v>
@@ -42738,7 +42738,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.9599187374115</v>
+        <v>2.95991897583008</v>
       </c>
       <c r="H1461" t="n">
         <v>1200</v>
@@ -43115,7 +43115,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.7974841594696</v>
+        <v>2.79748439788818</v>
       </c>
       <c r="H1474" t="n">
         <v>300</v>
@@ -43289,7 +43289,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.7974841594696</v>
+        <v>2.79748439788818</v>
       </c>
       <c r="H1480" t="n">
         <v>7200</v>
@@ -43347,7 +43347,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.7974841594696</v>
+        <v>2.79748439788818</v>
       </c>
       <c r="H1482" t="n">
         <v>3000</v>
@@ -43434,7 +43434,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.7974841594696</v>
+        <v>2.79748439788818</v>
       </c>
       <c r="H1485" t="n">
         <v>10500</v>
@@ -43579,7 +43579,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.7974841594696</v>
+        <v>2.79748439788818</v>
       </c>
       <c r="H1490" t="n">
         <v>4500</v>
@@ -43956,7 +43956,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.67114615440369</v>
+        <v>2.67114639282227</v>
       </c>
       <c r="H1503" t="n">
         <v>1200</v>
@@ -44101,7 +44101,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1508" t="n">
         <v>8400</v>
@@ -44130,7 +44130,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1509" t="n">
         <v>1800</v>
@@ -44565,7 +44565,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.63504958152771</v>
+        <v>2.63504981994629</v>
       </c>
       <c r="H1524" t="n">
         <v>5100</v>
@@ -44826,7 +44826,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1533" t="n">
         <v>7800</v>
@@ -44855,7 +44855,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1534" t="n">
         <v>6300</v>
@@ -44913,7 +44913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1536" t="n">
         <v>15900</v>
@@ -44942,7 +44942,7 @@
         <v>2.5</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1537" t="n">
         <v>7200</v>
@@ -44971,7 +44971,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1538" t="n">
         <v>300</v>
@@ -45000,7 +45000,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.27408409118652</v>
+        <v>2.27408385276794</v>
       </c>
       <c r="H1539" t="n">
         <v>9900</v>
@@ -45029,7 +45029,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1540" t="n">
         <v>9000</v>
@@ -45058,7 +45058,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1541" t="n">
         <v>0</v>
@@ -45087,7 +45087,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.27408409118652</v>
+        <v>2.27408385276794</v>
       </c>
       <c r="H1542" t="n">
         <v>900</v>
@@ -45116,7 +45116,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1543" t="n">
         <v>300</v>
@@ -45145,7 +45145,7 @@
         <v>2.5</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1544" t="n">
         <v>2400</v>
@@ -45174,7 +45174,7 @@
         <v>2.5</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.25603556632996</v>
+        <v>2.25603580474854</v>
       </c>
       <c r="H1545" t="n">
         <v>0</v>
@@ -45203,7 +45203,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.23798751831055</v>
+        <v>2.23798727989197</v>
       </c>
       <c r="H1546" t="n">
         <v>1500</v>
@@ -45232,7 +45232,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.23798751831055</v>
+        <v>2.23798727989197</v>
       </c>
       <c r="H1547" t="n">
         <v>0</v>
@@ -45261,7 +45261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.23798751831055</v>
+        <v>2.23798727989197</v>
       </c>
       <c r="H1548" t="n">
         <v>0</v>
@@ -45290,7 +45290,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1549" t="n">
         <v>600</v>
@@ -45319,7 +45319,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1550" t="n">
         <v>1500</v>
@@ -45348,7 +45348,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1551" t="n">
         <v>900</v>
@@ -45377,7 +45377,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1552" t="n">
         <v>0</v>
@@ -45406,7 +45406,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1553" t="n">
         <v>0</v>
@@ -45435,7 +45435,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1554" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1555" t="n">
         <v>0</v>
@@ -45493,7 +45493,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.32822871208191</v>
+        <v>2.32822895050049</v>
       </c>
       <c r="H1556" t="n">
         <v>2100</v>
@@ -45522,7 +45522,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.32822871208191</v>
+        <v>2.32822895050049</v>
       </c>
       <c r="H1557" t="n">
         <v>2100</v>
@@ -45551,7 +45551,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1558" t="n">
         <v>12600</v>
@@ -45696,7 +45696,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.36432528495789</v>
+        <v>2.36432552337646</v>
       </c>
       <c r="H1563" t="n">
         <v>18000</v>
@@ -45725,7 +45725,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1564" t="n">
         <v>8400</v>
@@ -45754,7 +45754,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1565" t="n">
         <v>8700</v>
@@ -45783,7 +45783,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1566" t="n">
         <v>4200</v>
@@ -45812,7 +45812,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.3101806640625</v>
+        <v>2.31018042564392</v>
       </c>
       <c r="H1567" t="n">
         <v>3900</v>
@@ -45841,7 +45841,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1568" t="n">
         <v>3300</v>
@@ -45870,7 +45870,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1569" t="n">
         <v>0</v>
@@ -45899,7 +45899,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1570" t="n">
         <v>0</v>
@@ -45928,7 +45928,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.29213213920593</v>
+        <v>2.29213237762451</v>
       </c>
       <c r="H1571" t="n">
         <v>1500</v>
@@ -45957,7 +45957,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.23798751831055</v>
+        <v>2.23798727989197</v>
       </c>
       <c r="H1572" t="n">
         <v>5100</v>
@@ -45986,7 +45986,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.21993899345398</v>
+        <v>2.21993923187256</v>
       </c>
       <c r="H1573" t="n">
         <v>1200</v>
@@ -46015,7 +46015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1574" t="n">
         <v>600</v>
@@ -46044,7 +46044,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1575" t="n">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1579" t="n">
         <v>600</v>
@@ -46189,7 +46189,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1580" t="n">
         <v>0</v>
@@ -46218,7 +46218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1581" t="n">
         <v>0</v>
@@ -46276,7 +46276,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.47261524200439</v>
+        <v>2.47261500358582</v>
       </c>
       <c r="H1583" t="n">
         <v>900</v>
@@ -46363,7 +46363,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1586" t="n">
         <v>3000</v>
@@ -46711,7 +46711,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1598" t="n">
         <v>3900</v>
@@ -46740,7 +46740,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1599" t="n">
         <v>0</v>
@@ -46769,7 +46769,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1600" t="n">
         <v>0</v>
@@ -46798,7 +46798,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1601" t="n">
         <v>0</v>
@@ -46827,7 +46827,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1602" t="n">
         <v>1800</v>
@@ -46856,7 +46856,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1603" t="n">
         <v>600</v>
@@ -46885,7 +46885,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.34627723693848</v>
+        <v>2.3462769985199</v>
       </c>
       <c r="H1604" t="n">
         <v>600</v>
@@ -47001,7 +47001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.57188081741333</v>
+        <v>2.57188057899475</v>
       </c>
       <c r="H1608" t="n">
         <v>1500</v>
@@ -47117,7 +47117,7 @@
         <v>2.75</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.48163914680481</v>
+        <v>2.48163938522339</v>
       </c>
       <c r="H1612" t="n">
         <v>3600</v>
@@ -47146,7 +47146,7 @@
         <v>2.75</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.48163914680481</v>
+        <v>2.48163938522339</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47407,7 +47407,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1622" t="n">
         <v>300</v>
@@ -47436,7 +47436,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1623" t="n">
         <v>0</v>
@@ -47465,7 +47465,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.43651866912842</v>
+        <v>2.43651843070984</v>
       </c>
       <c r="H1624" t="n">
         <v>0</v>
@@ -47900,7 +47900,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.44554257392883</v>
+        <v>2.44554281234741</v>
       </c>
       <c r="H1639" t="n">
         <v>5700</v>
@@ -48045,7 +48045,7 @@
         <v>2.75</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.48163914680481</v>
+        <v>2.48163938522339</v>
       </c>
       <c r="H1644" t="n">
         <v>5400</v>
@@ -80096,6 +80096,35 @@
         <v>3300</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H4" t="n">
         <v>2400</v>
@@ -514,7 +514,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H9" t="n">
         <v>300</v>
@@ -659,7 +659,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211312294006</v>
+        <v>2.23211288452148</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H12" t="n">
         <v>2700</v>
@@ -804,7 +804,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22874355316162</v>
+        <v>2.2287437915802</v>
       </c>
       <c r="H15" t="n">
         <v>300</v>
@@ -833,7 +833,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630507469177</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H16" t="n">
         <v>1500</v>
@@ -862,7 +862,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630507469177</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H18" t="n">
         <v>600</v>
@@ -920,7 +920,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157410621643</v>
       </c>
       <c r="H23" t="n">
         <v>300</v>
@@ -1065,7 +1065,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157410621643</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157410621643</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1239,7 +1239,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684385299683</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688208580017</v>
+        <v>2.36688184738159</v>
       </c>
       <c r="H36" t="n">
         <v>1500</v>
@@ -1616,7 +1616,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315173149109</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H43" t="n">
         <v>1800</v>
@@ -1645,7 +1645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315173149109</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H44" t="n">
         <v>12600</v>
@@ -1674,7 +1674,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315173149109</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315173149109</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630507469177</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H49" t="n">
         <v>1200</v>
@@ -2109,7 +2109,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630507469177</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H60" t="n">
         <v>235800</v>
@@ -2138,7 +2138,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630507469177</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H61" t="n">
         <v>2100</v>
@@ -2196,7 +2196,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745143890381</v>
+        <v>2.10745167732239</v>
       </c>
       <c r="H63" t="n">
         <v>900</v>
@@ -2225,7 +2225,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H64" t="n">
         <v>21600</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576677322388</v>
+        <v>2.10576701164246</v>
       </c>
       <c r="H70" t="n">
         <v>1200</v>
@@ -2428,7 +2428,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14788246154785</v>
+        <v>2.14788198471069</v>
       </c>
       <c r="H71" t="n">
         <v>24300</v>
@@ -2457,7 +2457,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.14788246154785</v>
+        <v>2.14788198471069</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.1782054901123</v>
+        <v>2.17820525169373</v>
       </c>
       <c r="H75" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H82" t="n">
         <v>6300</v>
@@ -2776,7 +2776,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H84" t="n">
         <v>6300</v>
@@ -2834,7 +2834,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G85" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H85" t="n">
         <v>3900</v>
@@ -2863,7 +2863,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G86" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G87" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H88" t="n">
         <v>300</v>
@@ -2950,7 +2950,7 @@
         <v>3</v>
       </c>
       <c r="G89" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692764282227</v>
       </c>
       <c r="H91" t="n">
         <v>2100</v>
@@ -3037,7 +3037,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692764282227</v>
       </c>
       <c r="H92" t="n">
         <v>2700</v>
@@ -3066,7 +3066,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692764282227</v>
       </c>
       <c r="H93" t="n">
         <v>2700</v>
@@ -3414,7 +3414,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.4666473865509</v>
+        <v>2.46664714813232</v>
       </c>
       <c r="H105" t="n">
         <v>1800</v>
@@ -3443,7 +3443,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.4666473865509</v>
+        <v>2.46664714813232</v>
       </c>
       <c r="H106" t="n">
         <v>2100</v>
@@ -3472,7 +3472,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.4666473865509</v>
+        <v>2.46664714813232</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H126" t="n">
         <v>4500</v>
@@ -4052,7 +4052,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H127" t="n">
         <v>300</v>
@@ -4081,7 +4081,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G140" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H140" t="n">
         <v>2400</v>
@@ -4458,7 +4458,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G142" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>2.10186147689819</v>
+        <v>2.10186123847961</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.10186147689819</v>
+        <v>2.10186123847961</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078305244446</v>
+        <v>1.91078317165375</v>
       </c>
       <c r="H152" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H157" t="n">
         <v>4200</v>
@@ -4951,7 +4951,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H158" t="n">
         <v>300</v>
@@ -5038,7 +5038,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95421004295349</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>1.84129977226257</v>
+        <v>1.84129989147186</v>
       </c>
       <c r="H163" t="n">
         <v>7200</v>
@@ -5125,7 +5125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>1.84129977226257</v>
+        <v>1.84129989147186</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H165" t="n">
         <v>3600</v>
@@ -5183,7 +5183,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G166" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G167" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H168" t="n">
         <v>9900</v>
@@ -5270,7 +5270,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H179" t="n">
         <v>3600</v>
@@ -5589,7 +5589,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H180" t="n">
         <v>8700</v>
@@ -5618,7 +5618,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138878822327</v>
+        <v>2.50138854980469</v>
       </c>
       <c r="H193" t="n">
         <v>25500</v>
@@ -6082,7 +6082,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G197" t="n">
-        <v>2.32941818237305</v>
+        <v>2.32941794395447</v>
       </c>
       <c r="H197" t="n">
         <v>1800</v>
@@ -6140,7 +6140,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64903998374939</v>
+        <v>2.64904022216797</v>
       </c>
       <c r="H199" t="n">
         <v>54000</v>
@@ -6169,7 +6169,7 @@
         <v>3</v>
       </c>
       <c r="G200" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H200" t="n">
         <v>28200</v>
@@ -6198,7 +6198,7 @@
         <v>3</v>
       </c>
       <c r="G201" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H201" t="n">
         <v>3600</v>
@@ -6256,7 +6256,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303117752075</v>
+        <v>2.58303141593933</v>
       </c>
       <c r="H203" t="n">
         <v>2400</v>
@@ -6575,7 +6575,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401761054993</v>
+        <v>2.48401784896851</v>
       </c>
       <c r="H214" t="n">
         <v>1200</v>
@@ -6604,7 +6604,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706937789917</v>
+        <v>2.47706961631775</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669415473938</v>
+        <v>2.42669463157654</v>
       </c>
       <c r="H216" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>2.37110805511475</v>
+        <v>2.37110829353333</v>
       </c>
       <c r="H219" t="n">
         <v>1200</v>
@@ -6778,7 +6778,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6865,7 +6865,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.37110805511475</v>
+        <v>2.37110829353333</v>
       </c>
       <c r="H224" t="n">
         <v>10500</v>
@@ -7068,7 +7068,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G231" t="n">
-        <v>2.20087432861328</v>
+        <v>2.20087456703186</v>
       </c>
       <c r="H231" t="n">
         <v>5700</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477150917053</v>
+        <v>2.21477127075195</v>
       </c>
       <c r="H232" t="n">
         <v>1800</v>
@@ -7126,7 +7126,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H233" t="n">
         <v>600</v>
@@ -7155,7 +7155,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H234" t="n">
         <v>8100</v>
@@ -7184,7 +7184,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G235" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H235" t="n">
         <v>1800</v>
@@ -7213,7 +7213,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>2.33462953567505</v>
+        <v>2.33462929725647</v>
       </c>
       <c r="H248" t="n">
         <v>9000</v>
@@ -7590,7 +7590,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G249" t="n">
-        <v>2.39542698860168</v>
+        <v>2.39542675018311</v>
       </c>
       <c r="H249" t="n">
         <v>3300</v>
@@ -7619,7 +7619,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H250" t="n">
         <v>6300</v>
@@ -7996,7 +7996,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>2.25124979019165</v>
+        <v>2.25125002861023</v>
       </c>
       <c r="H263" t="n">
         <v>8400</v>
@@ -8083,7 +8083,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H266" t="n">
         <v>1200</v>
@@ -8112,7 +8112,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H267" t="n">
         <v>600</v>
@@ -8141,7 +8141,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.33115530014038</v>
+        <v>2.33115553855896</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.33115530014038</v>
+        <v>2.33115553855896</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.33115530014038</v>
+        <v>2.33115553855896</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.33115530014038</v>
+        <v>2.33115553855896</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382863044739</v>
+        <v>2.64382886886597</v>
       </c>
       <c r="H277" t="n">
         <v>14700</v>
@@ -8547,7 +8547,7 @@
         <v>3</v>
       </c>
       <c r="G282" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H282" t="n">
         <v>18600</v>
@@ -8605,7 +8605,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955718040466</v>
+        <v>2.57955694198608</v>
       </c>
       <c r="H284" t="n">
         <v>12900</v>
@@ -8634,7 +8634,7 @@
         <v>3</v>
       </c>
       <c r="G285" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H285" t="n">
         <v>20400</v>
@@ -8663,7 +8663,7 @@
         <v>3</v>
       </c>
       <c r="G286" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.68378138542175</v>
+        <v>2.68378162384033</v>
       </c>
       <c r="H287" t="n">
         <v>10200</v>
@@ -8721,7 +8721,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.63166952133179</v>
+        <v>2.63166928291321</v>
       </c>
       <c r="H288" t="n">
         <v>900</v>
@@ -8750,7 +8750,7 @@
         <v>3</v>
       </c>
       <c r="G289" t="n">
-        <v>2.60561323165894</v>
+        <v>2.60561299324036</v>
       </c>
       <c r="H289" t="n">
         <v>8400</v>
@@ -8779,7 +8779,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772533416748</v>
+        <v>2.65772557258606</v>
       </c>
       <c r="H290" t="n">
         <v>35400</v>
@@ -8808,7 +8808,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>2.7706356048584</v>
+        <v>2.77063536643982</v>
       </c>
       <c r="H291" t="n">
         <v>11700</v>
@@ -8837,7 +8837,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.74110507965088</v>
+        <v>2.7411048412323</v>
       </c>
       <c r="H292" t="n">
         <v>21600</v>
@@ -8866,7 +8866,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537676811218</v>
+        <v>2.80537700653076</v>
       </c>
       <c r="H293" t="n">
         <v>7200</v>
@@ -8895,7 +8895,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706664085388</v>
+        <v>2.84706687927246</v>
       </c>
       <c r="H294" t="n">
         <v>10500</v>
@@ -8953,7 +8953,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110234260559</v>
+        <v>3.11110210418701</v>
       </c>
       <c r="H296" t="n">
         <v>15600</v>
@@ -8982,7 +8982,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044341087341</v>
+        <v>3.30044317245483</v>
       </c>
       <c r="H297" t="n">
         <v>20100</v>
@@ -9011,7 +9011,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.46546578407288</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H298" t="n">
         <v>8400</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.50889229774475</v>
+        <v>3.50889253616333</v>
       </c>
       <c r="H299" t="n">
         <v>17700</v>
@@ -9069,7 +9069,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020742416382</v>
+        <v>3.50020718574524</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.46546578407288</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H301" t="n">
         <v>8400</v>
@@ -9127,7 +9127,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124086380005</v>
+        <v>3.36124110221863</v>
       </c>
       <c r="H302" t="n">
         <v>18000</v>
@@ -9156,7 +9156,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23096036911011</v>
+        <v>3.23096060752869</v>
       </c>
       <c r="H303" t="n">
         <v>14700</v>
@@ -9330,7 +9330,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G309" t="n">
-        <v>3.13194704055786</v>
+        <v>3.13194727897644</v>
       </c>
       <c r="H309" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>3.23096036911011</v>
+        <v>3.23096060752869</v>
       </c>
       <c r="H311" t="n">
         <v>900</v>
@@ -9446,7 +9446,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>3.2396457195282</v>
+        <v>3.23964548110962</v>
       </c>
       <c r="H313" t="n">
         <v>3300</v>
@@ -9591,7 +9591,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>3.37861180305481</v>
+        <v>3.37861204147339</v>
       </c>
       <c r="H318" t="n">
         <v>7200</v>
@@ -9649,7 +9649,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34387040138245</v>
+        <v>3.34387016296387</v>
       </c>
       <c r="H320" t="n">
         <v>6300</v>
@@ -9678,7 +9678,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H321" t="n">
         <v>9300</v>
@@ -9707,7 +9707,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H322" t="n">
         <v>12300</v>
@@ -9736,7 +9736,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H323" t="n">
         <v>300</v>
@@ -9765,7 +9765,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218076705933</v>
+        <v>3.30218052864075</v>
       </c>
       <c r="H324" t="n">
         <v>1500</v>
@@ -9794,7 +9794,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>3.32649946212769</v>
+        <v>3.32649970054626</v>
       </c>
       <c r="H325" t="n">
         <v>3300</v>
@@ -9852,7 +9852,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G327" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H327" t="n">
         <v>2700</v>
@@ -9881,7 +9881,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H328" t="n">
         <v>3900</v>
@@ -9910,7 +9910,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H330" t="n">
         <v>15000</v>
@@ -9997,7 +9997,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588801383972</v>
+        <v>3.47588777542114</v>
       </c>
       <c r="H332" t="n">
         <v>900</v>
@@ -10026,7 +10026,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G333" t="n">
-        <v>3.47762513160706</v>
+        <v>3.47762537002563</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706092834473</v>
+        <v>3.58706068992615</v>
       </c>
       <c r="H334" t="n">
         <v>2700</v>
@@ -10113,7 +10113,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170783996582</v>
+        <v>3.7017080783844</v>
       </c>
       <c r="H336" t="n">
         <v>9300</v>
@@ -10171,7 +10171,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987670898438</v>
+        <v>3.77987623214722</v>
       </c>
       <c r="H338" t="n">
         <v>2100</v>
@@ -10200,7 +10200,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G339" t="n">
-        <v>3.78335022926331</v>
+        <v>3.78335046768188</v>
       </c>
       <c r="H339" t="n">
         <v>5400</v>
@@ -10229,7 +10229,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G340" t="n">
-        <v>3.78508734703064</v>
+        <v>3.78508710861206</v>
       </c>
       <c r="H340" t="n">
         <v>300</v>
@@ -10490,7 +10490,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G349" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H349" t="n">
         <v>1800</v>
@@ -10519,7 +10519,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G350" t="n">
-        <v>4.15473794937134</v>
+        <v>4.1547384262085</v>
       </c>
       <c r="H350" t="n">
         <v>4200</v>
@@ -10577,7 +10577,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H352" t="n">
         <v>4200</v>
@@ -10751,7 +10751,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>4.52930164337158</v>
+        <v>4.52930212020874</v>
       </c>
       <c r="H358" t="n">
         <v>16500</v>
@@ -10838,7 +10838,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G361" t="n">
-        <v>4.34246253967285</v>
+        <v>4.34246206283569</v>
       </c>
       <c r="H361" t="n">
         <v>9900</v>
@@ -10925,7 +10925,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>4.29464626312256</v>
+        <v>4.2946457862854</v>
       </c>
       <c r="H364" t="n">
         <v>300</v>
@@ -10954,7 +10954,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G365" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H365" t="n">
         <v>600</v>
@@ -10983,7 +10983,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G370" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H370" t="n">
         <v>2700</v>
@@ -11128,7 +11128,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H372" t="n">
         <v>5400</v>
@@ -11244,7 +11244,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H375" t="n">
         <v>2700</v>
@@ -11273,7 +11273,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H377" t="n">
         <v>900</v>
@@ -11447,7 +11447,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>4.33006525039673</v>
+        <v>4.33006572723389</v>
       </c>
       <c r="H382" t="n">
         <v>300</v>
@@ -11476,7 +11476,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G383" t="n">
-        <v>4.33006525039673</v>
+        <v>4.33006572723389</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G384" t="n">
-        <v>4.30881404876709</v>
+        <v>4.30881357192993</v>
       </c>
       <c r="H384" t="n">
         <v>600</v>
@@ -11563,7 +11563,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G386" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H386" t="n">
         <v>1200</v>
@@ -11621,7 +11621,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G388" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H388" t="n">
         <v>300</v>
@@ -11650,7 +11650,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G389" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G390" t="n">
-        <v>4.18661594390869</v>
+        <v>4.18661642074585</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11708,7 +11708,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H391" t="n">
         <v>2100</v>
@@ -11737,7 +11737,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G392" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H392" t="n">
         <v>300</v>
@@ -11766,7 +11766,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G393" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H395" t="n">
         <v>2700</v>
@@ -11853,7 +11853,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G396" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H396" t="n">
         <v>600</v>
@@ -12259,7 +12259,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>4.17067670822144</v>
+        <v>4.17067718505859</v>
       </c>
       <c r="H410" t="n">
         <v>3900</v>
@@ -12288,7 +12288,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>4.17067670822144</v>
+        <v>4.17067718505859</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.11754751205444</v>
+        <v>4.11754703521729</v>
       </c>
       <c r="H424" t="n">
         <v>6900</v>
@@ -12955,7 +12955,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>4.11754751205444</v>
+        <v>4.11754703521729</v>
       </c>
       <c r="H434" t="n">
         <v>1200</v>
@@ -13274,7 +13274,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G445" t="n">
-        <v>4.33006525039673</v>
+        <v>4.33006572723389</v>
       </c>
       <c r="H445" t="n">
         <v>600</v>
@@ -13361,7 +13361,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G448" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H448" t="n">
         <v>14700</v>
@@ -13593,7 +13593,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G456" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H456" t="n">
         <v>19800</v>
@@ -13680,7 +13680,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H459" t="n">
         <v>2400</v>
@@ -13796,7 +13796,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G463" t="n">
-        <v>4.15473794937134</v>
+        <v>4.1547384262085</v>
       </c>
       <c r="H463" t="n">
         <v>600</v>
@@ -14028,7 +14028,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>4.29464626312256</v>
+        <v>4.2946457862854</v>
       </c>
       <c r="H471" t="n">
         <v>12300</v>
@@ -14086,7 +14086,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H473" t="n">
         <v>3600</v>
@@ -14144,7 +14144,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H475" t="n">
         <v>9300</v>
@@ -14173,7 +14173,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G476" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H487" t="n">
         <v>2700</v>
@@ -14521,7 +14521,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G502" t="n">
-        <v>3.95107388496399</v>
+        <v>3.95107412338257</v>
       </c>
       <c r="H502" t="n">
         <v>3300</v>
@@ -15449,7 +15449,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H520" t="n">
         <v>1200</v>
@@ -15623,7 +15623,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H526" t="n">
         <v>34800</v>
@@ -15652,7 +15652,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H527" t="n">
         <v>24900</v>
@@ -15681,7 +15681,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H535" t="n">
         <v>600</v>
@@ -15942,7 +15942,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G537" t="n">
-        <v>3.8430438041687</v>
+        <v>3.84304404258728</v>
       </c>
       <c r="H537" t="n">
         <v>300</v>
@@ -16319,7 +16319,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>4.37434053421021</v>
+        <v>4.37434005737305</v>
       </c>
       <c r="H550" t="n">
         <v>27600</v>
@@ -16435,7 +16435,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H554" t="n">
         <v>18900</v>
@@ -16551,7 +16551,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H558" t="n">
         <v>2700</v>
@@ -16667,7 +16667,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>4.02014303207397</v>
+        <v>4.02014255523682</v>
       </c>
       <c r="H562" t="n">
         <v>5400</v>
@@ -16725,7 +16725,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H564" t="n">
         <v>6000</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H565" t="n">
         <v>4500</v>
@@ -16783,7 +16783,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H566" t="n">
         <v>4200</v>
@@ -16870,7 +16870,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H569" t="n">
         <v>2700</v>
@@ -16899,7 +16899,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H570" t="n">
         <v>3000</v>
@@ -16928,7 +16928,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H571" t="n">
         <v>4500</v>
@@ -16957,7 +16957,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H572" t="n">
         <v>21300</v>
@@ -17044,7 +17044,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H575" t="n">
         <v>18900</v>
@@ -17073,7 +17073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>4.60456848144531</v>
+        <v>4.60456895828247</v>
       </c>
       <c r="H576" t="n">
         <v>8100</v>
@@ -17218,7 +17218,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>4.37434053421021</v>
+        <v>4.37434005737305</v>
       </c>
       <c r="H581" t="n">
         <v>6000</v>
@@ -17276,7 +17276,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H583" t="n">
         <v>6600</v>
@@ -17334,7 +17334,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H585" t="n">
         <v>5100</v>
@@ -17363,7 +17363,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H586" t="n">
         <v>300</v>
@@ -17392,7 +17392,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H587" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H591" t="n">
         <v>2100</v>
@@ -17537,7 +17537,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>4.37434053421021</v>
+        <v>4.37434005737305</v>
       </c>
       <c r="H592" t="n">
         <v>7500</v>
@@ -17595,7 +17595,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G594" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H594" t="n">
         <v>300</v>
@@ -17624,7 +17624,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H595" t="n">
         <v>3000</v>
@@ -17653,7 +17653,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H596" t="n">
         <v>1200</v>
@@ -17682,7 +17682,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G599" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H602" t="n">
         <v>21300</v>
@@ -17856,7 +17856,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G603" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H603" t="n">
         <v>5700</v>
@@ -17885,7 +17885,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H604" t="n">
         <v>12300</v>
@@ -17943,7 +17943,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H606" t="n">
         <v>4800</v>
@@ -17972,7 +17972,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H607" t="n">
         <v>1500</v>
@@ -18001,7 +18001,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G608" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H608" t="n">
         <v>4500</v>
@@ -18030,7 +18030,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G614" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H614" t="n">
         <v>18000</v>
@@ -18262,7 +18262,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G617" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H617" t="n">
         <v>1200</v>
@@ -18291,7 +18291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G621" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H621" t="n">
         <v>6600</v>
@@ -18407,7 +18407,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H622" t="n">
         <v>10500</v>
@@ -18784,7 +18784,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G635" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H635" t="n">
         <v>2700</v>
@@ -18813,7 +18813,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G636" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G637" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G640" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H640" t="n">
         <v>1200</v>
@@ -18958,7 +18958,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G641" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H642" t="n">
         <v>9900</v>
@@ -19016,7 +19016,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H645" t="n">
         <v>600</v>
@@ -19103,7 +19103,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G646" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G647" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -19161,7 +19161,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G648" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G649" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G650" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H650" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H653" t="n">
         <v>300</v>
@@ -19393,7 +19393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G656" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H656" t="n">
         <v>900</v>
@@ -19422,7 +19422,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G657" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19538,7 +19538,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G662" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G664" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G665" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19712,7 +19712,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G667" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H667" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H669" t="n">
         <v>1200</v>
@@ -19799,7 +19799,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H670" t="n">
         <v>900</v>
@@ -19828,7 +19828,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G671" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G672" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H672" t="n">
         <v>300</v>
@@ -19886,7 +19886,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G673" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G674" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G677" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G681" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -20234,7 +20234,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.87846398353577</v>
+        <v>3.87846422195435</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20466,7 +20466,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G693" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H693" t="n">
         <v>1800</v>
@@ -20495,7 +20495,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G694" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H694" t="n">
         <v>2100</v>
@@ -20524,7 +20524,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G695" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H695" t="n">
         <v>3000</v>
@@ -20582,7 +20582,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H697" t="n">
         <v>3300</v>
@@ -20611,7 +20611,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>4.30350112915039</v>
+        <v>4.30350065231323</v>
       </c>
       <c r="H701" t="n">
         <v>2700</v>
@@ -20727,7 +20727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>4.39204978942871</v>
+        <v>4.39205026626587</v>
       </c>
       <c r="H702" t="n">
         <v>300</v>
@@ -20756,7 +20756,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H703" t="n">
         <v>5100</v>
@@ -20785,7 +20785,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G704" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H704" t="n">
         <v>2100</v>
@@ -20814,7 +20814,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H705" t="n">
         <v>3000</v>
@@ -20843,7 +20843,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H706" t="n">
         <v>3300</v>
@@ -20872,7 +20872,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H707" t="n">
         <v>3000</v>
@@ -20901,7 +20901,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G713" t="n">
-        <v>4.37434053421021</v>
+        <v>4.37434005737305</v>
       </c>
       <c r="H713" t="n">
         <v>2700</v>
@@ -21394,7 +21394,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G725" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H725" t="n">
         <v>300</v>
@@ -21423,7 +21423,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H728" t="n">
         <v>900</v>
@@ -21510,7 +21510,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H738" t="n">
         <v>900</v>
@@ -23105,7 +23105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H784" t="n">
         <v>600</v>
@@ -23134,7 +23134,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>3.94930338859558</v>
+        <v>3.94930362701416</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23366,7 +23366,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H793" t="n">
         <v>21300</v>
@@ -23395,7 +23395,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H794" t="n">
         <v>3000</v>
@@ -23743,7 +23743,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H806" t="n">
         <v>1500</v>
@@ -23772,7 +23772,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H807" t="n">
         <v>2700</v>
@@ -23801,7 +23801,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H809" t="n">
         <v>600</v>
@@ -23859,7 +23859,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.28579139709473</v>
+        <v>4.28579092025757</v>
       </c>
       <c r="H811" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H816" t="n">
         <v>300</v>
@@ -24236,7 +24236,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G823" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H823" t="n">
         <v>1200</v>
@@ -24265,7 +24265,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G824" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24294,7 +24294,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G825" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H825" t="n">
         <v>1800</v>
@@ -24700,7 +24700,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H839" t="n">
         <v>7800</v>
@@ -24729,7 +24729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G840" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G846" t="n">
-        <v>4.3212103843689</v>
+        <v>4.32121086120605</v>
       </c>
       <c r="H846" t="n">
         <v>300</v>
@@ -24932,7 +24932,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>4.25037145614624</v>
+        <v>4.2503719329834</v>
       </c>
       <c r="H847" t="n">
         <v>8400</v>
@@ -80125,6 +80125,35 @@
         <v>4200</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
